--- a/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication terrestrial results.xlsx
@@ -2426,7 +2426,7 @@
         <v>0.0004001981722826193</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0006668290790212192</v>
+        <v>0.0006668290790212194</v>
       </c>
       <c r="G6" t="n">
         <v>0.0005384672796431695</v>
@@ -3218,7 +3218,7 @@
         <v>0.0005345961062215156</v>
       </c>
       <c r="F15" t="n">
-        <v>0.000912332632675488</v>
+        <v>0.0009123326326754878</v>
       </c>
       <c r="G15" t="n">
         <v>0.0007461523655743517</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003291941411390201</v>
+        <v>0.00329194141139017</v>
       </c>
       <c r="C2" t="n">
         <v>0.001156469552318387</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004562559960383144</v>
+        <v>0.004562559960383111</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001922549803031484</v>
+        <v>0.001922549803031483</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00211726252637783</v>
+        <v>0.002117262526377831</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004150727060845465</v>
+        <v>0.004150727060845442</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001458637754016243</v>
+        <v>0.001458637754016223</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004429433159541706</v>
+        <v>0.004429433159541672</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004380963665846322</v>
+        <v>0.004380963665846272</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005191822967126171</v>
+        <v>0.005191822967126139</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003691081394191476</v>
+        <v>0.003691081394191412</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01205201315286395</v>
+        <v>0.01205201315286394</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002961954230551852</v>
+        <v>0.002961954230551828</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002885618488576306</v>
+        <v>0.002885618488576294</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004375963013555412</v>
+        <v>0.004375963013555399</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002119565085148923</v>
+        <v>0.002119565085148899</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001456890309693703</v>
+        <v>0.001456890309693681</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00396459695871407</v>
+        <v>0.003964596958714051</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00349774343460281</v>
+        <v>0.003497743434602779</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004210784666989152</v>
+        <v>0.004210784666989107</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002185230194765328</v>
+        <v>0.002185230194765326</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004027499882859277</v>
+        <v>0.004027499882859252</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004368989270358249</v>
+        <v>0.004368989270358213</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00526000116841542</v>
+        <v>0.005260001168415403</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.002401180521055918</v>
+        <v>0.002401180521055888</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004907372481934693</v>
+        <v>0.004907372481934657</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006971132975986936</v>
+        <v>0.006971132975986931</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004729411037272506</v>
+        <v>0.000472941103727214</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006391232406864054</v>
+        <v>0.0006391232406864068</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006436834827396622</v>
+        <v>0.0006436834827396825</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005380464018734011</v>
+        <v>0.0005380464018734022</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004911974863645285</v>
+        <v>0.0004911974863645291</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006790880273095501</v>
+        <v>0.0006790880273095578</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006436834827396622</v>
+        <v>0.0006436834827396825</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006436834827396622</v>
+        <v>0.0006436834827396825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006379193096166138</v>
+        <v>0.0006379193096166012</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006436834827396622</v>
+        <v>0.0006436834827396825</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006436834827396622</v>
+        <v>0.0006436834827396825</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006616945304572399</v>
+        <v>0.0006616945304572415</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005113295744214162</v>
+        <v>0.000511329574421403</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005477015776256975</v>
+        <v>0.0005477015776256941</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005387859207707212</v>
+        <v>0.0005387859207707328</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004393863292525076</v>
+        <v>0.0004393863292524652</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006436834827396622</v>
+        <v>0.0006436834827396825</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006436834827396622</v>
+        <v>0.0006436834827396825</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006436834827396622</v>
+        <v>0.0006436834827396825</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005602354213990556</v>
+        <v>0.0005602354213990385</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005805213503110974</v>
+        <v>0.0005805213503110931</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0006437170384871983</v>
+        <v>0.0006437170384871744</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004550352075456618</v>
+        <v>0.0004550352075456439</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008132588807862152</v>
+        <v>0.0008132588807862234</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004697694763795122</v>
+        <v>0.0004697694763795038</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0006436834827396622</v>
+        <v>0.0006436834827396825</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008310647043161721</v>
+        <v>0.0008310647043161717</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00525383399608274</v>
+        <v>0.005253833996082681</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004472581492053775</v>
+        <v>0.00447258149205374</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005716959536834361</v>
+        <v>0.005716959536834288</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004745350957870542</v>
+        <v>0.004745350957870532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004820375080998991</v>
+        <v>0.004820375080998938</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005566851280938963</v>
+        <v>0.005566851280938892</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004585616340708351</v>
+        <v>0.004585616340708309</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005668436381181487</v>
+        <v>0.005668436381181419</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005532903749627043</v>
+        <v>0.005532903749626969</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005946318513612905</v>
+        <v>0.005946318513612854</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005399315832875516</v>
+        <v>0.005399315832875405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008458223512214943</v>
+        <v>0.008458223512214858</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005133557543572264</v>
+        <v>0.005133557543572212</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005105734062001714</v>
+        <v>0.00510573406200167</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005648947140847633</v>
+        <v>0.005648947140847551</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004826516591905678</v>
+        <v>0.004826516591905595</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00458497941777233</v>
+        <v>0.004584979417772256</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005499009044362065</v>
+        <v>0.005499009044361966</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00532884641689438</v>
+        <v>0.005328846416894295</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005588741573146344</v>
+        <v>0.005588741573146289</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004078113118480668</v>
+        <v>0.004078113118480681</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005521936421569555</v>
+        <v>0.005521936421569488</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005646405293342093</v>
+        <v>0.005646405293342063</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005971168667393979</v>
+        <v>0.005971168667393916</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004929162111398367</v>
+        <v>0.004929162111398279</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005842639651946854</v>
+        <v>0.00584263965194678</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00660059258360455</v>
+        <v>0.006600592583604444</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004226341486312424</v>
+        <v>0.004226341486312397</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004284014836451021</v>
+        <v>0.004284014836450963</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00428857507850428</v>
+        <v>0.00428857507850421</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00424071572580817</v>
+        <v>0.004240715725808177</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004227693468133921</v>
+        <v>0.004227693468133798</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004301479619258818</v>
+        <v>0.004301479619258804</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00428857507850428</v>
+        <v>0.00428857507850421</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00428857507850428</v>
+        <v>0.00428857507850421</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004168608034827164</v>
+        <v>0.004168608034827165</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00428857507850428</v>
+        <v>0.00428857507850421</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00428857507850428</v>
+        <v>0.00428857507850421</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004306586126221832</v>
+        <v>0.004306586126221753</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004240333633100357</v>
+        <v>0.004240333633100265</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004253590801166681</v>
+        <v>0.004253590801166615</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004250341148935962</v>
+        <v>0.00425034114893588</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004214111165036461</v>
+        <v>0.004214111165036388</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00428857507850428</v>
+        <v>0.00428857507850421</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00428857507850428</v>
+        <v>0.00428857507850421</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00428857507850428</v>
+        <v>0.00428857507850421</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004258159240042181</v>
+        <v>0.004258159240042195</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003493215588119736</v>
+        <v>0.003493215588119781</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004288587309180229</v>
+        <v>0.004288587309180142</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004219814997415959</v>
+        <v>0.00421981499741586</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004350383319837344</v>
+        <v>0.004350383319837301</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004225185465387414</v>
+        <v>0.00422518546538729</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.00428857507850428</v>
+        <v>0.00428857507850421</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004362609798902321</v>
+        <v>0.004362609798902319</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001371842641588806</v>
+        <v>0.001371842641588795</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005905901375598073</v>
+        <v>0.0005905901375598079</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001834968182340432</v>
+        <v>0.00183496818234042</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008633596033766323</v>
+        <v>0.0008633596033766339</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009383837265050379</v>
+        <v>0.000938383726505039</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001642675384058485</v>
+        <v>0.001642675384058449</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0007036249862144314</v>
+        <v>0.0007036249862144219</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001786445026687554</v>
+        <v>0.001786445026687539</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001724616949314094</v>
+        <v>0.001724616949314084</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002064327159118977</v>
+        <v>0.002064327159118971</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001517324478381561</v>
+        <v>0.001517324478381536</v>
       </c>
       <c r="M6" t="n">
-        <v>0.004576232157720988</v>
+        <v>0.004576232157720983</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001251566189078339</v>
+        <v>0.001251566189078336</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001181558165121243</v>
+        <v>0.001181558165121226</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00172477124396715</v>
+        <v>0.00172477124396714</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009445252374117353</v>
+        <v>0.0009445252374117225</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0007029880632783935</v>
+        <v>0.0007029880632783813</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001617017689868133</v>
+        <v>0.001617017689868119</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001446855062400431</v>
+        <v>0.001446855062400426</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001664565676265826</v>
+        <v>0.001664565676265809</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009184645815952459</v>
+        <v>0.0009184645815952508</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001597760524689083</v>
+        <v>0.001597760524689069</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001722229396461611</v>
+        <v>0.001722229396461594</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002089177312900057</v>
+        <v>0.002089177312900042</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001047170756904431</v>
+        <v>0.001047170756904414</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001960648297452917</v>
+        <v>0.001960648297452908</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002718601229110555</v>
+        <v>0.002718601229110556</v>
       </c>
     </row>
     <row r="7">
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003443501318185403</v>
+        <v>0.0003443501318185258</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0004020234819570543</v>
+        <v>0.0004020234819570548</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004065837240103178</v>
+        <v>0.0004065837240103173</v>
       </c>
       <c r="E7" t="n">
         <v>0.0003587243713142627</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003457021136399165</v>
+        <v>0.0003457021136399167</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003773037223783288</v>
+        <v>0.000377303722378358</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004065837240103178</v>
+        <v>0.0004065837240103173</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004065837240103178</v>
+        <v>0.0004065837240103173</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003603212345143163</v>
+        <v>0.0003603212345142786</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004065837240103178</v>
+        <v>0.0004065837240103173</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004065837240103178</v>
+        <v>0.0004065837240103173</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0004245947717278468</v>
+        <v>0.0004245947717278472</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003583422786063946</v>
+        <v>0.0003583422786063517</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003294149042861761</v>
+        <v>0.0003294149042861648</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003261652520554814</v>
+        <v>0.0003261652520554576</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003321198105425191</v>
+        <v>0.0003321198105425382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0004065837240103178</v>
+        <v>0.0004065837240103173</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004065837240103178</v>
+        <v>0.0004065837240103173</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004065837240103178</v>
+        <v>0.0004065837240103173</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0003339833431617136</v>
+        <v>0.0003339833431617301</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003335670512342955</v>
+        <v>0.0003335670512342974</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003644114122997133</v>
+        <v>0.0003644114122997157</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002956391005354786</v>
+        <v>0.0002956391005354471</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004683919653434039</v>
+        <v>0.0004683919653434359</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003431941108934322</v>
+        <v>0.0003431941108933953</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0004065837240103178</v>
+        <v>0.0004065837240103173</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004806184444084033</v>
+        <v>0.0004806184444084038</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="M8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="P8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="R8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0007072270046025353</v>
+        <v>0.0007072270046025367</v>
       </c>
       <c r="T8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="U8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="W8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="X8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.000704266365701691</v>
+        <v>0.0007042663657016921</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003561333857996539</v>
+        <v>0.003561333857996517</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001271236772088578</v>
+        <v>0.001271236772088579</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004926871411553379</v>
+        <v>0.004926871411553388</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002105466165377825</v>
+        <v>0.002105466165377828</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002307869500963624</v>
+        <v>0.002307869500963625</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004484273363103191</v>
+        <v>0.004484273363103198</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001591076936120637</v>
+        <v>0.001591076936120638</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004783799640660432</v>
+        <v>0.004783799640660431</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004737904104959019</v>
+        <v>0.004737904104959015</v>
       </c>
       <c r="K9" t="n">
-        <v>0.005603142246299775</v>
+        <v>0.005603142246299782</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003990290790880278</v>
+        <v>0.003990290790880272</v>
       </c>
       <c r="M9" t="n">
-        <v>0.012956452622994</v>
+        <v>0.01295645262299399</v>
       </c>
       <c r="N9" t="n">
-        <v>0.003206695648138635</v>
+        <v>0.003206695648138632</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003124657398005379</v>
+        <v>0.003124657398005383</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004726335114901456</v>
+        <v>0.004726335114901455</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002301377514960048</v>
+        <v>0.002301377514960052</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001589198952482615</v>
+        <v>0.001589198952482616</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004284238785842185</v>
+        <v>0.004284238785842187</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003782509907659542</v>
+        <v>0.003782509907659536</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004548817451988813</v>
+        <v>0.004548817451988828</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002389544388047588</v>
+        <v>0.002389544388047597</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004351840746491111</v>
+        <v>0.004351840746491109</v>
       </c>
       <c r="X9" t="n">
-        <v>0.004718840412237031</v>
+        <v>0.004718840412237038</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005676413563067683</v>
+        <v>0.005676413563067685</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00260403046591616</v>
+        <v>0.002604030465916157</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.005297442459401286</v>
+        <v>0.005297442459401278</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.007505671194473471</v>
+        <v>0.007505671194473466</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0005317457989736012</v>
+        <v>0.0005317457989736014</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0006175362207009014</v>
+        <v>0.000617536220700902</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0005603325407768256</v>
+        <v>0.0005603325407768273</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0007532925140951526</v>
+        <v>0.0007532925140951536</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0007152431441918139</v>
+        <v>0.0007152431441918145</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0005730020032042747</v>
+        <v>0.000573002003204276</v>
       </c>
       <c r="O10" t="n">
         <v>0.0006120911037946159</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0006025094207161439</v>
+        <v>0.0006025094207161454</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.00049568438252197</v>
+        <v>0.0004956843825219706</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0006255612631720976</v>
+        <v>0.0006255612631720983</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006649589950798696</v>
+        <v>0.0006649589950798701</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0007152792066539141</v>
+        <v>0.0007152792066539149</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0005125022788113832</v>
+        <v>0.000512502278811384</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0008974863314767347</v>
+        <v>0.0008974863314767348</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0005283372415803318</v>
+        <v>0.0005283372415803324</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0007152431441917415</v>
+        <v>0.0007152431441917425</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0009069214650486698</v>
+        <v>0.00090692146504867</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="J11" t="n">
-        <v>0.003745790176844506</v>
+        <v>0.003745790176844384</v>
       </c>
       <c r="K11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="M11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="O11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="R11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="S11" t="n">
-        <v>0.00384544541172455</v>
+        <v>0.003845445411724483</v>
       </c>
       <c r="T11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="V11" t="n">
-        <v>0.003188825527281318</v>
+        <v>0.003188825527281266</v>
       </c>
       <c r="W11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.003843990182404913</v>
+        <v>0.003843990182404783</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.005248311520551204</v>
+        <v>0.00524831152055118</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004122670557276648</v>
+        <v>0.004122670557276577</v>
       </c>
       <c r="D12" t="n">
-        <v>0.005919507958742336</v>
+        <v>0.005919507958742281</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004532715521585116</v>
+        <v>0.004532715521585019</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0046322019088831</v>
+        <v>0.004632201908883109</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005701959761040757</v>
+        <v>0.005701959761040736</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004279880132604396</v>
+        <v>0.004279880132604301</v>
       </c>
       <c r="I12" t="n">
-        <v>0.005849184544509664</v>
+        <v>0.005849184544509604</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00572842571586048</v>
+        <v>0.005728425715860412</v>
       </c>
       <c r="K12" t="n">
-        <v>0.006251912274062715</v>
+        <v>0.006251912274062672</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005459154763008367</v>
+        <v>0.005459154763008327</v>
       </c>
       <c r="M12" t="n">
-        <v>0.009866251345804421</v>
+        <v>0.009866251345804319</v>
       </c>
       <c r="N12" t="n">
-        <v>0.00507399782065836</v>
+        <v>0.005073997820658308</v>
       </c>
       <c r="O12" t="n">
-        <v>0.005033673934184912</v>
+        <v>0.005033673934184843</v>
       </c>
       <c r="P12" t="n">
-        <v>0.005820939268565935</v>
+        <v>0.00582093926856585</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.00462901093264741</v>
+        <v>0.004629010932647379</v>
       </c>
       <c r="R12" t="n">
-        <v>0.00427895705588232</v>
+        <v>0.004278957055882251</v>
       </c>
       <c r="S12" t="n">
-        <v>0.00560363767870554</v>
+        <v>0.005603637678705506</v>
       </c>
       <c r="T12" t="n">
-        <v>0.005357025174277049</v>
+        <v>0.005357025174276978</v>
       </c>
       <c r="U12" t="n">
-        <v>0.00573368482232045</v>
+        <v>0.005733684822320377</v>
       </c>
       <c r="V12" t="n">
-        <v>0.004017182538052652</v>
+        <v>0.004017182538052668</v>
       </c>
       <c r="W12" t="n">
-        <v>0.005636865761729783</v>
+        <v>0.005636865761729712</v>
       </c>
       <c r="X12" t="n">
-        <v>0.005817255431588618</v>
+        <v>0.005817255431588569</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.006287926989811904</v>
+        <v>0.006287926989811845</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.004777772555614643</v>
+        <v>0.004777772555614591</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.006101653053737636</v>
+        <v>0.006101653053737594</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.007187053640364629</v>
+        <v>0.007187053640364572</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.003759191936028591</v>
+        <v>0.003759191936028489</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003801360110271997</v>
+        <v>0.003801360110271933</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003773243046690324</v>
+        <v>0.003773243046690313</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003868087781254667</v>
+        <v>0.003868087781254608</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="I13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00375118554265198</v>
+        <v>0.003751185542651918</v>
       </c>
       <c r="K13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="M13" t="n">
-        <v>0.003849385548212438</v>
+        <v>0.003849385548212329</v>
       </c>
       <c r="N13" t="n">
-        <v>0.003779470409704221</v>
+        <v>0.003779470409704144</v>
       </c>
       <c r="O13" t="n">
-        <v>0.003798683696823281</v>
+        <v>0.003798683696823258</v>
       </c>
       <c r="P13" t="n">
-        <v>0.003793974055892944</v>
+        <v>0.003793974055892854</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.003741466832668777</v>
+        <v>0.003741466832668774</v>
       </c>
       <c r="R13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="S13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="T13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="U13" t="n">
-        <v>0.003805304622752749</v>
+        <v>0.003805304622752755</v>
       </c>
       <c r="V13" t="n">
-        <v>0.003169504954890383</v>
+        <v>0.003169504954890347</v>
       </c>
       <c r="W13" t="n">
-        <v>0.003849403273829758</v>
+        <v>0.003849403273829696</v>
       </c>
       <c r="X13" t="n">
-        <v>0.003749733256435737</v>
+        <v>0.003749733256435649</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.003938962709874236</v>
+        <v>0.003938962709874234</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.003757516543377663</v>
+        <v>0.003757516543377614</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003849385548212402</v>
+        <v>0.003849385548212291</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.003943600317994828</v>
+        <v>0.003943600317994808</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004696988592458544</v>
+        <v>0.0004696988592458548</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0004711487987856138</v>
+        <v>0.0004711487987856143</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0004696988592458544</v>
+        <v>0.0004696988592458548</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0004696988592458544</v>
+        <v>0.0004696988592458548</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0005074274206196351</v>
+        <v>0.0005074274206196355</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0004696988592458544</v>
+        <v>0.0004696988592458548</v>
       </c>
       <c r="V14" t="n">
         <v>0.0004719303313528011</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0004696988592458544</v>
+        <v>0.0004696988592458548</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0004696988592458544</v>
+        <v>0.0004696988592458548</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0005059721912999856</v>
+        <v>0.0005059721912999863</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.001910293529446294</v>
+        <v>0.001910293529446296</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0007846525661717244</v>
+        <v>0.0007846525661717257</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00258148996763743</v>
+        <v>0.002581489967637428</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001194697530480199</v>
+        <v>0.001194697530480202</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001294183917778252</v>
+        <v>0.001294183917778251</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002327668437881731</v>
+        <v>0.00232766843788172</v>
       </c>
       <c r="H15" t="n">
-        <v>0.000941862141499489</v>
+        <v>0.000941862141499491</v>
       </c>
       <c r="I15" t="n">
-        <v>0.002511166553404753</v>
+        <v>0.002511166553404754</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00245378433780169</v>
+        <v>0.002453784337801681</v>
       </c>
       <c r="K15" t="n">
         <v>0.002913894282957808</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00212113677190346</v>
+        <v>0.002121136771903446</v>
       </c>
       <c r="M15" t="n">
-        <v>0.006528233354699511</v>
+        <v>0.006528233354699506</v>
       </c>
       <c r="N15" t="n">
-        <v>0.001735979829553453</v>
+        <v>0.001735979829553452</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001659382611025861</v>
+        <v>0.001659382611025865</v>
       </c>
       <c r="P15" t="n">
-        <v>0.002446647945406866</v>
+        <v>0.002446647945406869</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.00129099294154253</v>
+        <v>0.001290992941542529</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0009409390647774073</v>
+        <v>0.0009409390647774068</v>
       </c>
       <c r="S15" t="n">
-        <v>0.002265619687600625</v>
+        <v>0.002265619687600622</v>
       </c>
       <c r="T15" t="n">
         <v>0.002019007183172118</v>
       </c>
       <c r="U15" t="n">
-        <v>0.002359393499161422</v>
+        <v>0.002359393499161417</v>
       </c>
       <c r="V15" t="n">
-        <v>0.001300287342124152</v>
+        <v>0.001300287342124151</v>
       </c>
       <c r="W15" t="n">
-        <v>0.002262574438570729</v>
+        <v>0.002262574438570731</v>
       </c>
       <c r="X15" t="n">
-        <v>0.002442964108429586</v>
+        <v>0.002442964108429589</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.002949908998706996</v>
+        <v>0.002949908998706997</v>
       </c>
       <c r="Z15" t="n">
         <v>0.001439754564509731</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.002763635062632727</v>
+        <v>0.002763635062632724</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.003849035649259725</v>
+        <v>0.003849035649259726</v>
       </c>
     </row>
     <row r="16">
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0004211739449236802</v>
+        <v>0.0004211739449236809</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0004633421191670724</v>
+        <v>0.0004633421191670729</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0004352250555854395</v>
+        <v>0.0004352250555854401</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004937964580956337</v>
+        <v>0.0004937964580956342</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0004765441645931271</v>
+        <v>0.0004765441645931277</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0005113675571075338</v>
+        <v>0.0005113675571075344</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0004414524185993312</v>
+        <v>0.000441452418599332</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0004243923736642491</v>
+        <v>0.0004243923736642498</v>
       </c>
       <c r="P16" t="n">
-        <v>0.00041968273273391</v>
+        <v>0.0004196827327339108</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0004034488415638965</v>
+        <v>0.0004034488415638967</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0004310132995937362</v>
+        <v>0.0004310132995937367</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0004526097589618728</v>
+        <v>0.0004526097589618733</v>
       </c>
       <c r="W16" t="n">
-        <v>0.000475111950670726</v>
+        <v>0.0004751119506707262</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0003754419332766692</v>
+        <v>0.0003754419332766697</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0006009447187693469</v>
+        <v>0.0006009447187693475</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0004194985522727989</v>
+        <v>0.0004194985522727995</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0005113675571074981</v>
+        <v>0.0005113675571074986</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.000605582326889933</v>
+        <v>0.0006055823268899338</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002848947726453504</v>
+        <v>0.002848947726453506</v>
       </c>
       <c r="C2" t="n">
         <v>0.001041227118947209</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003123128907899079</v>
+        <v>0.003123128907899056</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00136781064536625</v>
+        <v>0.001367810645366253</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002383736899836471</v>
+        <v>0.002383736899836464</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003773721392353557</v>
+        <v>0.003773721392353526</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001419059932088987</v>
+        <v>0.001419059932088997</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004140893929793052</v>
+        <v>0.004140893929793051</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004090434488398148</v>
+        <v>0.004090434488398131</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006031072525237701</v>
+        <v>0.006031072525237712</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003289389212812713</v>
+        <v>0.003289389212812705</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01004788744583554</v>
+        <v>0.01004788744583552</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002032538638739125</v>
+        <v>0.002032538638739119</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002740430357329621</v>
+        <v>0.002740430357329612</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003908425090301674</v>
+        <v>0.003908425090301673</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00200988365833967</v>
+        <v>0.002009883658339666</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002085582229832776</v>
+        <v>0.002085582229832766</v>
       </c>
       <c r="S2" t="n">
         <v>0.003717455744508722</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003743103084071576</v>
+        <v>0.003743103084071571</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004157829225056004</v>
+        <v>0.004157829225055992</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002995380470428247</v>
+        <v>0.002995380470428236</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002653046589766866</v>
+        <v>0.002653046589766873</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004718578632200647</v>
+        <v>0.004718578632200638</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007661002269914899</v>
+        <v>0.007661002269914885</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.002097359588555254</v>
+        <v>0.002097359588555253</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00526661609947169</v>
+        <v>0.005266616099471677</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006415043674791193</v>
+        <v>0.006415043674791181</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004655567214621587</v>
+        <v>0.0004655567214621395</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006305230431172778</v>
+        <v>0.0006305230431172768</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006341439497370375</v>
+        <v>0.0006341439497370354</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005300630209493947</v>
+        <v>0.000530063020949393</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004857467154609619</v>
+        <v>0.0004857467154609612</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006691016097620304</v>
+        <v>0.0006691016097620559</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006341439497370375</v>
+        <v>0.0006341439497370354</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006341439497370375</v>
+        <v>0.0006341439497370354</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006293795959392343</v>
+        <v>0.0006293795959392399</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006341439497370375</v>
+        <v>0.0006341439497370354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006341439497370375</v>
+        <v>0.0006341439497370354</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006479078166152569</v>
+        <v>0.0006479078166152561</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005034606437894518</v>
+        <v>0.0005034606437894254</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000539373550957091</v>
+        <v>0.00053937355095709</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000530570429633967</v>
+        <v>0.0005305704296339746</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000432425483296027</v>
+        <v>0.0004324254832960369</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006341439497370375</v>
+        <v>0.0006341439497370354</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006341439497370375</v>
+        <v>0.0006341439497370354</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006341439497370375</v>
+        <v>0.0006341439497370354</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005517498498848764</v>
+        <v>0.0005517498498848907</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005745449859017876</v>
+        <v>0.0005745449859017759</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0006341770819364631</v>
+        <v>0.0006341770819364616</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004478768377422445</v>
+        <v>0.0004478768377422308</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008015800565349095</v>
+        <v>0.0008015800565349206</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004624251271457694</v>
+        <v>0.0004624251271457925</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0006341439497370375</v>
+        <v>0.0006341439497370354</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008188112820518232</v>
+        <v>0.0008188112820518219</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005063376175856497</v>
+        <v>0.005063376175856585</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004402182113071857</v>
+        <v>0.004402182113071915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005163311996895429</v>
+        <v>0.005163311996895421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004514422893769667</v>
+        <v>0.00451442289376973</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004889952241138943</v>
+        <v>0.004889952241138979</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00540044531783642</v>
+        <v>0.005400445317836421</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004542198865400837</v>
+        <v>0.004542198865400877</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005534275396175506</v>
+        <v>0.005534275396175544</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005407345628346758</v>
+        <v>0.005407345628346803</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006223223298617398</v>
+        <v>0.006223223298617443</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005223911925709378</v>
+        <v>0.005223911925709385</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007696052268377651</v>
+        <v>0.00769605226837768</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004765804650144131</v>
+        <v>0.004765804650144136</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005023822869086131</v>
+        <v>0.005023822869086121</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005449543233967821</v>
+        <v>0.005449543233967818</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004757547175816737</v>
+        <v>0.004757547175816745</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004785138416228467</v>
+        <v>0.004785138416228503</v>
       </c>
       <c r="S4" t="n">
         <v>0.005379937149901572</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005389285304005965</v>
+        <v>0.005389285304005975</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005540448112434567</v>
+        <v>0.005540448112434569</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004404296235982171</v>
+        <v>0.004404296235982157</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004991972511921508</v>
+        <v>0.004991972511921586</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005744834686686815</v>
+        <v>0.005744834686686817</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006817313550950857</v>
+        <v>0.006817313550950858</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004789431125186087</v>
+        <v>0.004789431125186074</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005944587908126244</v>
+        <v>0.005944587908126329</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006368618717170282</v>
+        <v>0.006368618717170258</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004194658141727343</v>
+        <v>0.004194658141727362</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004252485300162603</v>
+        <v>0.004252485300162642</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004256106206782358</v>
+        <v>0.004256106206782407</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00420907372199899</v>
+        <v>0.004209073721999042</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004198157106260049</v>
+        <v>0.004198157106260107</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004268847863367891</v>
+        <v>0.004268847863367949</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004256106206782358</v>
+        <v>0.004256106206782407</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004256106206782358</v>
+        <v>0.004256106206782407</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004145831761803949</v>
+        <v>0.004145831761803965</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004256106206782358</v>
+        <v>0.004256106206782407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004256106206782358</v>
+        <v>0.004256106206782407</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004269870073660508</v>
+        <v>0.004269870073660567</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004208473676325318</v>
+        <v>0.004208473676325345</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004221563509277276</v>
+        <v>0.004221563509277299</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004218354874926465</v>
+        <v>0.004218354874926481</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00418258219446243</v>
+        <v>0.004182582194462515</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004256106206782358</v>
+        <v>0.004256106206782407</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004256106206782358</v>
+        <v>0.004256106206782407</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004256106206782358</v>
+        <v>0.004256106206782407</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004226074524906613</v>
+        <v>0.004226074524906675</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003521930128757753</v>
+        <v>0.003521930128757746</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004256118283079992</v>
+        <v>0.004256118283080075</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004188214031719111</v>
+        <v>0.00418821403171912</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004317134701576142</v>
+        <v>0.004317134701576204</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004193516712372065</v>
+        <v>0.00419351671237204</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004256106206782358</v>
+        <v>0.004256106206782407</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004328857724295317</v>
+        <v>0.0043288577242953</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001207716168900957</v>
+        <v>0.001207716168900956</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005465221061163188</v>
+        <v>0.0005465221061163184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001307651989939891</v>
+        <v>0.001307651989939872</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006587628868141263</v>
+        <v>0.000658762886814127</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001034292234183403</v>
+        <v>0.0010342922341834</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001502723952254806</v>
+        <v>0.001502723952254787</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0006865388584452947</v>
+        <v>0.0006865388584452979</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001678615389219968</v>
+        <v>0.001678615389219954</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001616804494948239</v>
+        <v>0.00161680449494825</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002367563291661853</v>
+        <v>0.00236756329166187</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001368251918753831</v>
+        <v>0.001368251918753816</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003840392261422105</v>
+        <v>0.003840392261422101</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009101446431885914</v>
+        <v>0.0009101446431885787</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001126101503504513</v>
+        <v>0.001126101503504501</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001551821868386213</v>
+        <v>0.001551821868386192</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000901887168861201</v>
+        <v>0.0009018871688611861</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0009294784092729317</v>
+        <v>0.0009294784092729217</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001524277142946033</v>
+        <v>0.00152427714294602</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001533625297050427</v>
+        <v>0.001533625297050416</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001642726746852962</v>
+        <v>0.001642726746852947</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001213070644187808</v>
+        <v>0.001213070644187799</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001094251146339894</v>
+        <v>0.001094251146339936</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001847113321105196</v>
+        <v>0.001847113321105179</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002961653543995328</v>
+        <v>0.002961653543995305</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009337711182305487</v>
+        <v>0.0009337711182305372</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002088927901170718</v>
+        <v>0.002088927901170729</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002512958710214759</v>
+        <v>0.002512958710214753</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003389981347718063</v>
+        <v>0.0003389981347718237</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003968252932070561</v>
+        <v>0.0003968252932070559</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004004461998268162</v>
+        <v>0.0004004461998268403</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003534137150434536</v>
+        <v>0.0003534137150434531</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003424970993045131</v>
+        <v>0.0003424970993045127</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003711264977862849</v>
+        <v>0.0003711264977862922</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004004461998268162</v>
+        <v>0.0004004461998268403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004004461998268162</v>
+        <v>0.0004004461998268403</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003552906284054311</v>
+        <v>0.0003552906284054398</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004004461998268162</v>
+        <v>0.0004004461998268403</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004004461998268162</v>
+        <v>0.0004004461998268403</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000414210066704973</v>
+        <v>0.0004142100667049724</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003528136693697762</v>
+        <v>0.0003528136693697522</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003238421436956613</v>
+        <v>0.000323842143695647</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003206335093448523</v>
+        <v>0.0003206335093448507</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003269221875068917</v>
+        <v>0.0003269221875068933</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0004004461998268162</v>
+        <v>0.0004004461998268403</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004004461998268162</v>
+        <v>0.0004004461998268403</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004004461998268162</v>
+        <v>0.0004004461998268403</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0003283531593249982</v>
+        <v>0.0003283531593249908</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003307045369633874</v>
+        <v>0.0003307045369633879</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003583969174983771</v>
+        <v>0.0003583969174984018</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002904926661375008</v>
+        <v>0.0002904926661374762</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004614746946206074</v>
+        <v>0.0004614746946206063</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003378567054165187</v>
+        <v>0.0003378567054164927</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0004004461998268162</v>
+        <v>0.0004004461998268403</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004731977173397754</v>
+        <v>0.0004731977173397743</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570921</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0006836834825640131</v>
+        <v>0.0006836834825640134</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0006800762971570929</v>
+        <v>0.0006800762971570916</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00308811128881309</v>
+        <v>0.003088111288813097</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00114923994628957</v>
+        <v>0.001149239946289568</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003382774624272249</v>
+        <v>0.003382774624272238</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001511711281183607</v>
+        <v>0.001511711281183609</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002594675488802688</v>
+        <v>0.002594675488802674</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004081968312486984</v>
+        <v>0.004081968312486958</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001551406601064859</v>
+        <v>0.001551406601064855</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004476569736262665</v>
+        <v>0.004476569736262663</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004427461089000761</v>
+        <v>0.004427461089000754</v>
       </c>
       <c r="K9" t="n">
-        <v>0.006507950324130434</v>
+        <v>0.00650795032413043</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003561455071055662</v>
+        <v>0.003561455071055663</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01081004126007032</v>
+        <v>0.01081004126007031</v>
       </c>
       <c r="N9" t="n">
-        <v>0.002210714001308788</v>
+        <v>0.002210714001308786</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002971487347765408</v>
+        <v>0.002971487347765403</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004226734779415163</v>
+        <v>0.004226734779415168</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002186366626138581</v>
+        <v>0.002186366626138583</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002267720107249315</v>
+        <v>0.002267720107249313</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004021499452522493</v>
+        <v>0.00402149945252249</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004049062725032295</v>
+        <v>0.004049062725032296</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004494770148715685</v>
+        <v>0.004494770148715672</v>
       </c>
       <c r="V9" t="n">
-        <v>0.003259885513220134</v>
+        <v>0.003259885513220128</v>
       </c>
       <c r="W9" t="n">
-        <v>0.002877575751501684</v>
+        <v>0.002877575751501681</v>
       </c>
       <c r="X9" t="n">
         <v>0.005097409213128532</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.008259640693974401</v>
+        <v>0.008259640693974373</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002280377269880857</v>
+        <v>0.002280377269880858</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.005686386717752534</v>
+        <v>0.005686386717752536</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.006911401644109257</v>
+        <v>0.00691140164410924</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0005266738497761807</v>
+        <v>0.0005266738497761798</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0006113814044861974</v>
+        <v>0.0006113814044861963</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0005548997629554395</v>
+        <v>0.0005548997629554391</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0007454241497999787</v>
+        <v>0.0007454241497999775</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0007078550480531955</v>
+        <v>0.0007078550480531945</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0005674093084282238</v>
+        <v>0.0005674093084282227</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0006060050171353573</v>
+        <v>0.0006060050171353555</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0005965442763294167</v>
+        <v>0.0005965442763294151</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0004910676090617297</v>
+        <v>0.0004910676090617287</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="U10" t="n">
-        <v>0.000619305862596281</v>
+        <v>0.0006193058625962795</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0006582063800735933</v>
+        <v>0.0006582063800735914</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0007078906553268725</v>
+        <v>0.0007078906553268708</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0005076732258822544</v>
+        <v>0.0005076732258822529</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.000887799132636982</v>
+        <v>0.0008877991326369799</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0005233083160013723</v>
+        <v>0.0005233083160013716</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0007078550480530897</v>
+        <v>0.0007078550480530881</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0008971139597576686</v>
+        <v>0.0008971139597576676</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="J11" t="n">
-        <v>0.003717901857379559</v>
+        <v>0.003717901857379573</v>
       </c>
       <c r="K11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="L11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459832</v>
       </c>
       <c r="M11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="N11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="O11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="R11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="S11" t="n">
-        <v>0.003810400202831207</v>
+        <v>0.003810400202831251</v>
       </c>
       <c r="T11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="V11" t="n">
-        <v>0.003203331719027783</v>
+        <v>0.003203331719027815</v>
       </c>
       <c r="W11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="X11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.003808627179459782</v>
+        <v>0.003808627179459828</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.004992237623002111</v>
+        <v>0.004992237623002121</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004039233045557163</v>
+        <v>0.004039233045557204</v>
       </c>
       <c r="D12" t="n">
-        <v>0.005137072146747387</v>
+        <v>0.005137072146747448</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004217396925630295</v>
+        <v>0.004217396925630348</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004749701377418594</v>
+        <v>0.004749701377418649</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00548074362755952</v>
+        <v>0.005480743627559558</v>
       </c>
       <c r="H12" t="n">
-        <v>0.004236908184949205</v>
+        <v>0.004236908184949256</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00567470026350375</v>
+        <v>0.005674700263503752</v>
       </c>
       <c r="J12" t="n">
-        <v>0.005559836792281654</v>
+        <v>0.005559836792281675</v>
       </c>
       <c r="K12" t="n">
-        <v>0.006673175487884091</v>
+        <v>0.006673175487884157</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005224898130839192</v>
+        <v>0.00522489813083924</v>
       </c>
       <c r="M12" t="n">
-        <v>0.008787762600816996</v>
+        <v>0.008787762600817036</v>
       </c>
       <c r="N12" t="n">
-        <v>0.004560974540769389</v>
+        <v>0.004560974540769448</v>
       </c>
       <c r="O12" t="n">
-        <v>0.004934913989803503</v>
+        <v>0.00493491398980354</v>
       </c>
       <c r="P12" t="n">
-        <v>0.005551900027995829</v>
+        <v>0.005551900027995873</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.004549007186630371</v>
+        <v>0.004549007186630416</v>
       </c>
       <c r="R12" t="n">
-        <v>0.004588994491713078</v>
+        <v>0.00458899449171306</v>
       </c>
       <c r="S12" t="n">
-        <v>0.005451021644942549</v>
+        <v>0.005451021644942597</v>
       </c>
       <c r="T12" t="n">
-        <v>0.005464569694416019</v>
+        <v>0.005464569694416066</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0056836462291275</v>
+        <v>0.005683646229127553</v>
       </c>
       <c r="V12" t="n">
-        <v>0.004471373562713512</v>
+        <v>0.004471373562713446</v>
       </c>
       <c r="W12" t="n">
-        <v>0.004888754051724268</v>
+        <v>0.004888754051724251</v>
       </c>
       <c r="X12" t="n">
-        <v>0.005979858656603544</v>
+        <v>0.005979858656603587</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.007534175856559814</v>
+        <v>0.007534175856559838</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.004595215809064454</v>
+        <v>0.004595215809064516</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.006269356079979863</v>
+        <v>0.006269356079979929</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.006871482072897421</v>
+        <v>0.006871482072897464</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.003733225974986363</v>
+        <v>0.003733225974986376</v>
       </c>
       <c r="C13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="D13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003774861892549486</v>
+        <v>0.003774861892549518</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003747099729202246</v>
+        <v>0.003747099729202264</v>
       </c>
       <c r="G13" t="n">
-        <v>0.003840747311068828</v>
+        <v>0.003840747311068869</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="I13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00373155581996026</v>
+        <v>0.003731555819960275</v>
       </c>
       <c r="K13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="M13" t="n">
-        <v>0.00382228114204052</v>
+        <v>0.003822281142040543</v>
       </c>
       <c r="N13" t="n">
-        <v>0.003753248488965637</v>
+        <v>0.003753248488965624</v>
       </c>
       <c r="O13" t="n">
-        <v>0.003772219261425337</v>
+        <v>0.003772219261425344</v>
       </c>
       <c r="P13" t="n">
-        <v>0.003767569066697952</v>
+        <v>0.003767569066697996</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.003715724602078195</v>
+        <v>0.003715724602078233</v>
       </c>
       <c r="R13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="S13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="T13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="U13" t="n">
-        <v>0.003778756965258562</v>
+        <v>0.00377875696525859</v>
       </c>
       <c r="V13" t="n">
-        <v>0.003192582098549258</v>
+        <v>0.003192582098549239</v>
       </c>
       <c r="W13" t="n">
-        <v>0.003822298643921154</v>
+        <v>0.003822298643921174</v>
       </c>
       <c r="X13" t="n">
-        <v>0.003723886685087088</v>
+        <v>0.003723886685087103</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.003910728236250126</v>
+        <v>0.003910728236250161</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.003731571729538196</v>
+        <v>0.003731571729538211</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.003822281142040468</v>
+        <v>0.003822281142040492</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.003915306710690093</v>
+        <v>0.003915306710690162</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0004570833828555565</v>
+        <v>0.0004570833828555559</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0004585194913352011</v>
+        <v>0.0004585194913352003</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0004570833828555565</v>
+        <v>0.0004570833828555559</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0004570833828555565</v>
+        <v>0.0004570833828555559</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0004950238159409743</v>
+        <v>0.0004950238159409739</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0004570833828555565</v>
+        <v>0.0004570833828555559</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0004592842788599167</v>
+        <v>0.000459284278859916</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0004570833828555565</v>
+        <v>0.0004570833828555559</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0004570833828555565</v>
+        <v>0.0004570833828555559</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0004932507925695462</v>
+        <v>0.0004932507925695455</v>
       </c>
     </row>
     <row r="15">
@@ -7634,85 +7634,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.001676861236111874</v>
+        <v>0.001676861236111878</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0007238566586669252</v>
+        <v>0.0007238566586669246</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001821695759857163</v>
+        <v>0.001821695759857156</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0009020205387400603</v>
+        <v>0.0009020205387400605</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00143432499052836</v>
+        <v>0.001434324990528356</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002129199830955295</v>
+        <v>0.002129199830955284</v>
       </c>
       <c r="H15" t="n">
         <v>0.0009215317980589697</v>
       </c>
       <c r="I15" t="n">
-        <v>0.00235932387661351</v>
+        <v>0.002359323876613513</v>
       </c>
       <c r="J15" t="n">
-        <v>0.002300454426237301</v>
+        <v>0.002300454426237298</v>
       </c>
       <c r="K15" t="n">
-        <v>0.003357799100993865</v>
+        <v>0.003357799100993869</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001909521743948955</v>
+        <v>0.001909521743948957</v>
       </c>
       <c r="M15" t="n">
-        <v>0.005472386213926764</v>
+        <v>0.005472386213926757</v>
       </c>
       <c r="N15" t="n">
-        <v>0.001245598153879156</v>
+        <v>0.001245598153879155</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001583370193199277</v>
+        <v>0.001583370193199275</v>
       </c>
       <c r="P15" t="n">
-        <v>0.002200356231391609</v>
+        <v>0.002200356231391602</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.001233630799740138</v>
+        <v>0.001233630799740136</v>
       </c>
       <c r="R15" t="n">
-        <v>0.001273618104822844</v>
+        <v>0.001273618104822845</v>
       </c>
       <c r="S15" t="n">
-        <v>0.002135645258052317</v>
+        <v>0.002135645258052315</v>
       </c>
       <c r="T15" t="n">
         <v>0.002149193307525788</v>
       </c>
       <c r="U15" t="n">
-        <v>0.002332102432523284</v>
+        <v>0.002332102432523281</v>
       </c>
       <c r="V15" t="n">
-        <v>0.001727326122545543</v>
+        <v>0.001727326122545541</v>
       </c>
       <c r="W15" t="n">
-        <v>0.001537210255120046</v>
+        <v>0.001537210255120041</v>
       </c>
       <c r="X15" t="n">
-        <v>0.002628314859999315</v>
+        <v>0.002628314859999313</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.004218799469669588</v>
+        <v>0.004218799469669573</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.001279839422174222</v>
+        <v>0.001279839422174221</v>
       </c>
       <c r="AA15" t="n">
         <v>0.002953979693089632</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.003556105686007173</v>
+        <v>0.003556105686007172</v>
       </c>
     </row>
     <row r="16">
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0004178495880961264</v>
+        <v>0.000417849588096126</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0004594855056592513</v>
+        <v>0.0004594855056592503</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0004317233423120137</v>
+        <v>0.0004317233423120129</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0004892035144646041</v>
+        <v>0.0004892035144646031</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0004721734539158922</v>
+        <v>0.0004721734539158912</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0005069047551502873</v>
+        <v>0.0005069047551502865</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0004378721020754138</v>
+        <v>0.0004378721020754132</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0004206754648211159</v>
+        <v>0.0004206754648211151</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0004160252700937305</v>
+        <v>0.0004160252700937299</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0004003482151879513</v>
+        <v>0.0004003482151879505</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0004272131686543424</v>
+        <v>0.0004272131686543414</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0004485346583813405</v>
+        <v>0.0004485346583813394</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0004707548473169332</v>
+        <v>0.0004707548473169322</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0003723428884828636</v>
+        <v>0.0003723428884828631</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.000595351849359897</v>
+        <v>0.0005953518493598958</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0004161953426479663</v>
+        <v>0.0004161953426479654</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.0005069047551502352</v>
+        <v>0.0005069047551502342</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0005999303237998611</v>
+        <v>0.0005999303237998596</v>
       </c>
     </row>
   </sheetData>
@@ -9627,7 +9627,7 @@
         <v>0.004191534841757013</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004458511635416318</v>
+        <v>0.004458511635416319</v>
       </c>
       <c r="F4" t="n">
         <v>0.00446181123485662</v>
@@ -9751,7 +9751,7 @@
         <v>0.004027907711756376</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003995329629503597</v>
+        <v>0.003995329629503598</v>
       </c>
       <c r="R5" t="n">
         <v>0.004062287746418162</v>
@@ -9778,7 +9778,7 @@
         <v>0.004117864773275324</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004005287665055615</v>
+        <v>0.004005287665055616</v>
       </c>
       <c r="AA5" t="n">
         <v>0.004062287746418162</v>
@@ -9854,7 +9854,7 @@
         <v>0.00035605522400549</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0006490434783444011</v>
+        <v>0.000649043478344401</v>
       </c>
       <c r="W6" t="n">
         <v>0.001133087230595353</v>
@@ -9866,7 +9866,7 @@
         <v>0.0006873395721008855</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008503849554035503</v>
+        <v>0.00085038495540355</v>
       </c>
       <c r="AA6" t="n">
         <v>0.0009617238451180693</v>
@@ -10115,7 +10115,7 @@
         <v>0.001115668528576025</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0007532494364539013</v>
+        <v>0.0007532494364539012</v>
       </c>
       <c r="V9" t="n">
         <v>0.001644008406828841</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.003857756296178867</v>
+        <v>0.003857756296178866</v>
       </c>
       <c r="C12" t="n">
         <v>0.003864635144961301</v>
@@ -10337,7 +10337,7 @@
         <v>0.004226410351868036</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00404510023064227</v>
+        <v>0.004045100230642269</v>
       </c>
       <c r="H12" t="n">
         <v>0.004120383656024255</v>
@@ -10352,7 +10352,7 @@
         <v>0.003931288345911319</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004240779231969992</v>
+        <v>0.004240779231969991</v>
       </c>
       <c r="M12" t="n">
         <v>0.003771807721997447</v>
@@ -10361,10 +10361,10 @@
         <v>0.00423218920420503</v>
       </c>
       <c r="O12" t="n">
-        <v>0.004262062527919988</v>
+        <v>0.004262062527919987</v>
       </c>
       <c r="P12" t="n">
-        <v>0.004177767018373866</v>
+        <v>0.004177767018373867</v>
       </c>
       <c r="Q12" t="n">
         <v>0.003752458328474366</v>
@@ -10373,10 +10373,10 @@
         <v>0.004846728090310151</v>
       </c>
       <c r="S12" t="n">
-        <v>0.004193559244705005</v>
+        <v>0.004193559244705006</v>
       </c>
       <c r="T12" t="n">
-        <v>0.003876802853605818</v>
+        <v>0.003876802853605817</v>
       </c>
       <c r="U12" t="n">
         <v>0.003698664652183811</v>
@@ -10400,7 +10400,7 @@
         <v>0.004515964678978622</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.003577586098072661</v>
+        <v>0.003577586098072662</v>
       </c>
     </row>
     <row r="13">
@@ -10449,7 +10449,7 @@
         <v>0.003577927745798076</v>
       </c>
       <c r="O13" t="n">
-        <v>0.003595204376388268</v>
+        <v>0.003595204376388267</v>
       </c>
       <c r="P13" t="n">
         <v>0.003590969456769061</v>
@@ -10649,7 +10649,7 @@
         <v>0.0009174837170925314</v>
       </c>
       <c r="W15" t="n">
-        <v>0.001603575799594874</v>
+        <v>0.001603575799594875</v>
       </c>
       <c r="X15" t="n">
         <v>0.002478590651200155</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide eutrophication terrestrial results.xlsx
@@ -586,82 +586,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00520826201757564</v>
+        <v>0.005208262017575619</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001334680307873657</v>
+        <v>0.001334680307873656</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004653962804160481</v>
+        <v>0.004653962804160455</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002025510239178071</v>
+        <v>0.002025510239178064</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003440968306927028</v>
+        <v>0.003440968306927025</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004703668216934508</v>
+        <v>0.00470366821693448</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004220655079786266</v>
+        <v>0.004220655079786233</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005384748046956246</v>
+        <v>0.005384748046956275</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004858829796405451</v>
+        <v>0.004858829796405447</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008348689171558761</v>
+        <v>0.008348689171558727</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00503988494431914</v>
+        <v>0.005039884944319122</v>
       </c>
       <c r="M2" t="n">
         <v>0.01514575168456175</v>
       </c>
       <c r="N2" t="n">
-        <v>0.006157326778471042</v>
+        <v>0.006157326778471011</v>
       </c>
       <c r="O2" t="n">
-        <v>0.004823985910283988</v>
+        <v>0.004823985910283967</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004133566004171644</v>
+        <v>0.004133566004171619</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003047061259085206</v>
+        <v>0.003047061259085196</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003441853457576477</v>
+        <v>0.003441853457576454</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004531601255539159</v>
+        <v>0.004531601255539137</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00552544831006662</v>
+        <v>0.005525448310066595</v>
       </c>
       <c r="U2" t="n">
-        <v>0.007233404122883215</v>
+        <v>0.007233404122883196</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002825477277688228</v>
+        <v>0.002825477277688224</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004025850788509864</v>
+        <v>0.004025850788509843</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003092438184200562</v>
+        <v>0.00309243818420052</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.003649586376862909</v>
+        <v>0.003649586376862871</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00307258414797748</v>
+        <v>0.003072584147977479</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.006290392071971199</v>
+        <v>0.006290392071971157</v>
       </c>
       <c r="AB2" t="n">
         <v>0.007881945353692738</v>
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005186219336670158</v>
+        <v>0.0005186219336670464</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006951974789766113</v>
+        <v>0.0006951974789766112</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007017387417390817</v>
+        <v>0.0007017387417390364</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005858945891426759</v>
+        <v>0.0005858945891426755</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005400372070672546</v>
+        <v>0.0005400372070672543</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007397092047863537</v>
+        <v>0.0007397092047863257</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007017387417390817</v>
+        <v>0.0007017387417390364</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007017387417390817</v>
+        <v>0.0007017387417390364</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006951432400303726</v>
+        <v>0.0006951432400303498</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007017387417390817</v>
+        <v>0.0007017387417390364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007017387417390817</v>
+        <v>0.0007017387417390364</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007251698952983979</v>
+        <v>0.0007251698952983975</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005597925807026956</v>
+        <v>0.0005597925807026934</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005988006182420176</v>
+        <v>0.0005988006182419287</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000589238805675983</v>
+        <v>0.0005892388056759362</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004826353014494401</v>
+        <v>0.000482635301449423</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007017387417390817</v>
+        <v>0.0007017387417390364</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007017387417390817</v>
+        <v>0.0007017387417390364</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007017387417390817</v>
+        <v>0.0007017387417390364</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006123027094557341</v>
+        <v>0.0006123027094557883</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000632649460093596</v>
+        <v>0.0006326494600935962</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0007017747294163569</v>
+        <v>0.000701774729416319</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004994183207542389</v>
+        <v>0.0004994183207542534</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008837064065386764</v>
+        <v>0.0008837064065386751</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0005152204449464217</v>
+        <v>0.0005152204449463978</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0007017387417390817</v>
+        <v>0.0007017387417390364</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.000901891566611668</v>
+        <v>0.0009018915666116678</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006036298591457711</v>
+        <v>0.006036298591457675</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004620266494867333</v>
+        <v>0.004620266494867311</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005834263037077876</v>
+        <v>0.005834263037077834</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004864567749472645</v>
+        <v>0.004864567749472624</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005387620909350089</v>
+        <v>0.00538762090935007</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00585238007636358</v>
+        <v>0.005852380076363543</v>
       </c>
       <c r="H4" t="n">
-        <v>0.005676327459699665</v>
+        <v>0.005676327459699627</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006100625676763368</v>
+        <v>0.006100625676763317</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005803377846993201</v>
+        <v>0.005803377846993199</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007180947412327095</v>
+        <v>0.007180947412327055</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005974927125439143</v>
+        <v>0.005974927125439108</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009673287656408385</v>
+        <v>0.00967328765640837</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006382221552322992</v>
+        <v>0.006382221552323027</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005896234462747784</v>
+        <v>0.005896234462747746</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005644584514289697</v>
+        <v>0.005644584514289657</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.005248566293088545</v>
+        <v>0.005248566293088505</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005392463413554561</v>
+        <v>0.005392463413554523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005789663689447254</v>
+        <v>0.005789663689447219</v>
       </c>
       <c r="T4" t="n">
-        <v>0.006151909270481191</v>
+        <v>0.006151909270481151</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006774439108423114</v>
+        <v>0.006774439108423074</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004479459321566819</v>
+        <v>0.004479459321566817</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005605323583036894</v>
+        <v>0.005605323583036856</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005265105649450342</v>
+        <v>0.005265105649450274</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005468179623311374</v>
+        <v>0.005468179623311276</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.005257869086384885</v>
+        <v>0.005257869086384845</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.006430722289272254</v>
+        <v>0.00643072228927221</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.007016463036052256</v>
+        <v>0.007016463036052236</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004326979849407189</v>
+        <v>0.004326979849407148</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004387182512920855</v>
+        <v>0.004387182512920837</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004393723775683321</v>
+        <v>0.004393723775683327</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004339844749855193</v>
+        <v>0.00433984474985517</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004330265587904013</v>
+        <v>0.004330265587903995</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004407563563592374</v>
+        <v>0.004407563563592324</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004393723775683321</v>
+        <v>0.004393723775683327</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004393723775683321</v>
+        <v>0.004393723775683327</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004285762989670501</v>
+        <v>0.004285762989670515</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004393723775683321</v>
+        <v>0.004393723775683327</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004393723775683321</v>
+        <v>0.004393723775683327</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004417154929242635</v>
+        <v>0.004417154929242612</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004341986066801543</v>
+        <v>0.004341986066801472</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004356204038429123</v>
+        <v>0.00435620403842906</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004352718870029273</v>
+        <v>0.004352718870029211</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004313863144540244</v>
+        <v>0.004313863144540261</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004393723775683321</v>
+        <v>0.004393723775683327</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004393723775683321</v>
+        <v>0.004393723775683327</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004393723775683321</v>
+        <v>0.004393723775683327</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004361125392126964</v>
+        <v>0.004361125392126931</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003680199331537847</v>
+        <v>0.003680199331537846</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004393736892769103</v>
+        <v>0.004393736892769076</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00431998035800068</v>
+        <v>0.004319980358000606</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004460048852730577</v>
+        <v>0.00446004885273053</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004325740046710822</v>
+        <v>0.004325740046710802</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004393723775683321</v>
+        <v>0.004393723775683327</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004472315394590958</v>
+        <v>0.004472315394590939</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002088271281026723</v>
+        <v>0.002088271281026708</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006722391844363329</v>
+        <v>0.0006722391844363331</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001886235726646882</v>
+        <v>0.001886235726646861</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009165404390416528</v>
+        <v>0.0009165404390416514</v>
       </c>
       <c r="F6" t="n">
         <v>0.001439593598919089</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001860869815812749</v>
+        <v>0.001860869815812729</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001728300149268667</v>
+        <v>0.001728300149268645</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002152598366332366</v>
+        <v>0.002152598366332337</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001915024547669392</v>
+        <v>0.001915024547669373</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003232920101896094</v>
+        <v>0.003232920101896077</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002026899815008141</v>
+        <v>0.002026899815008133</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005725260345977388</v>
+        <v>0.005725260345977392</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002434194241892007</v>
+        <v>0.002434194241892061</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001904724202196951</v>
+        <v>0.001904724202196934</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00165307425373886</v>
+        <v>0.001653074253738841</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001300538982657552</v>
+        <v>0.001300538982657536</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001444436103123566</v>
+        <v>0.001444436103123543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001841636379016262</v>
+        <v>0.001841636379016246</v>
       </c>
       <c r="T6" t="n">
-        <v>0.002203881960050191</v>
+        <v>0.002203881960050172</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002782928847872264</v>
+        <v>0.00278292884787225</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001167041402689531</v>
+        <v>0.001167041402689529</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00161381332248606</v>
+        <v>0.001613813322486045</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001273595388899503</v>
+        <v>0.001273595388899465</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001520152312880381</v>
+        <v>0.001520152312880303</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001309841775953891</v>
+        <v>0.001309841775953874</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002482694978841256</v>
+        <v>0.002482694978841239</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.003068435725621261</v>
+        <v>0.003068435725621262</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003789525389761852</v>
+        <v>0.0003789525389761686</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0004391552024898602</v>
+        <v>0.0004391552024898599</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004456964652523306</v>
+        <v>0.0004456964652523507</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003918174394242044</v>
+        <v>0.000391817439424204</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003822382774730196</v>
+        <v>0.0003822382774730193</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000416053303041535</v>
+        <v>0.0004160533030415081</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004456964652523306</v>
+        <v>0.0004456964652523507</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004456964652523306</v>
+        <v>0.0004456964652523507</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003974096903466972</v>
+        <v>0.0003974096903467117</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004456964652523306</v>
+        <v>0.0004456964652523507</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004456964652523306</v>
+        <v>0.0004456964652523507</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000469127618811641</v>
+        <v>0.0004691276188116403</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003939587563705452</v>
+        <v>0.0003939587563704951</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003646937778782866</v>
+        <v>0.0003646937778782417</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003612086094784389</v>
+        <v>0.0003612086094783963</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003658358341092494</v>
+        <v>0.0003658358341092822</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0004456964652523306</v>
+        <v>0.0004456964652523507</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004456964652523306</v>
+        <v>0.0004456964652523507</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004456964652523306</v>
+        <v>0.0004456964652523507</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0003696151315761267</v>
+        <v>0.0003696151315761137</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000367781412660558</v>
+        <v>0.0003677814126605577</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0004022266322182709</v>
+        <v>0.0004022266322182647</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0003284700974498482</v>
+        <v>0.0003284700974497905</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0005120215422995808</v>
+        <v>0.0005120215422995565</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003777127362798259</v>
+        <v>0.0003777127362798243</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0004456964652523306</v>
+        <v>0.0004456964652523507</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0005242880841599641</v>
+        <v>0.0005242880841599638</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0005579694109647308</v>
+        <v>0.0005579694109646429</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009680910464885704</v>
+        <v>0.0009680910464885715</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009082474178393331</v>
+        <v>0.000908247417839237</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007097255578104312</v>
+        <v>0.0007097255578104304</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001430798095513228</v>
+        <v>0.001430798095513227</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001187157357813255</v>
+        <v>0.001187157357813188</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001063464755340949</v>
+        <v>0.001063464755340863</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001042698246018283</v>
+        <v>0.001042698246018192</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001393930733733183</v>
+        <v>0.001393930733733144</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001491881510883555</v>
+        <v>0.001491881510883465</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002342807674328508</v>
+        <v>0.002342807674328358</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00110103221662065</v>
+        <v>0.001101032216620647</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001377734291981214</v>
+        <v>0.001377734291981247</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001970104549439785</v>
+        <v>0.001970104549439665</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001483220879334625</v>
+        <v>0.001483220879334606</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008308802936967209</v>
+        <v>0.0008308802936966299</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002749780717573899</v>
+        <v>0.002749780717573816</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00181746589975119</v>
+        <v>0.001817465899751108</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001351432040979808</v>
+        <v>0.001351432040979757</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001234938029948599</v>
+        <v>0.001234938029948507</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001453542862357953</v>
+        <v>0.001453542862357954</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00235157731932693</v>
+        <v>0.00235157731932687</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004688788387501842</v>
+        <v>0.004688788387501737</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.002887520718272968</v>
+        <v>0.002887520718272866</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001146624911135505</v>
+        <v>0.001146624911135439</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00285507875892562</v>
+        <v>0.002855078758925511</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0005609612556415654</v>
+        <v>0.0005609612556415651</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004070715898295134</v>
+        <v>0.0004070715898294184</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005612613656003042</v>
+        <v>0.0005612613656003039</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005599783282229833</v>
+        <v>0.000559978328222972</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004693440437839754</v>
+        <v>0.0004693440437839755</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004276694202821729</v>
+        <v>0.0004276694202821721</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005916845365225716</v>
+        <v>0.000591684536522553</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005599783282229833</v>
+        <v>0.000559978328222972</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005599783282229833</v>
+        <v>0.000559978328222972</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005559057632417953</v>
+        <v>0.0005559057632417366</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005599783282229833</v>
+        <v>0.000559978328222972</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005599783282229833</v>
+        <v>0.000559978328222972</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005546049391827637</v>
+        <v>0.0005546049391827628</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004414500252237678</v>
+        <v>0.0004414500252236985</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0004740226320441188</v>
+        <v>0.0004740226320440454</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004660382990487732</v>
+        <v>0.0004660382990486625</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000377021925813099</v>
+        <v>0.0003770219258130646</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005599783282229833</v>
+        <v>0.000559978328222972</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005599783282229833</v>
+        <v>0.000559978328222972</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005599783282229833</v>
+        <v>0.000559978328222972</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004852428474637703</v>
+        <v>0.0004852428474637238</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000508605379489816</v>
+        <v>0.0005086053794898151</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0005600083787627094</v>
+        <v>0.0005600083787626628</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0003910361322077671</v>
+        <v>0.000391036132207651</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007118325444789451</v>
+        <v>0.0007118325444789063</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004042312686624968</v>
+        <v>0.0004042312686624168</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0005599783282229833</v>
+        <v>0.000559978328222972</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007140469758494204</v>
+        <v>0.00071404697584942</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004033903592165054</v>
+        <v>0.004033903592164945</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004184203497741429</v>
+        <v>0.004184203497741497</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004161575812498815</v>
+        <v>0.004161575812498679</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004083360076968524</v>
+        <v>0.004083360076968556</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004349990983707117</v>
+        <v>0.004349990983707152</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004263235210493447</v>
+        <v>0.004263235210493296</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004218150709364165</v>
+        <v>0.004218150709364055</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00421058156056872</v>
+        <v>0.004210581560568611</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004235990130326209</v>
+        <v>0.004235990130326231</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004374303586035917</v>
+        <v>0.004374303586035801</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004684456180532035</v>
+        <v>0.00468445618053196</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004228428756028546</v>
+        <v>0.004228428756028565</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004332698265130253</v>
+        <v>0.004332698265130257</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004548610268011217</v>
+        <v>0.004548610268011117</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004371146887534552</v>
+        <v>0.004371146887534515</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004133376404239483</v>
+        <v>0.004133376404239369</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004832793075876306</v>
+        <v>0.004832793075876187</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004492975272573217</v>
+        <v>0.00449297527257314</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004323111403496878</v>
+        <v>0.00432311140349684</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004280650704417801</v>
+        <v>0.004280650704417688</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003686983017822691</v>
+        <v>0.003686983017822694</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004687652613155662</v>
+        <v>0.004687652613155557</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005539538602587412</v>
+        <v>0.005539538602587305</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004882997688706339</v>
+        <v>0.004882997688706264</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004248461609635403</v>
+        <v>0.004248461609635324</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004871172975476954</v>
+        <v>0.004871172975476871</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004031400121592144</v>
+        <v>0.004031400121592177</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003978903108292865</v>
+        <v>0.003978903108292841</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004035918856293025</v>
+        <v>0.004035918856293039</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004034635818915697</v>
+        <v>0.004034635818915707</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003995743837808196</v>
+        <v>0.003995743837808161</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003984362360917005</v>
+        <v>0.003984362360917052</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004046192359527843</v>
+        <v>0.004046192359527818</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004034635818915697</v>
+        <v>0.004034635818915707</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004034635818915697</v>
+        <v>0.004034635818915707</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003930539869168141</v>
+        <v>0.003930539869168138</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004034635818915697</v>
+        <v>0.004034635818915707</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004034635818915697</v>
+        <v>0.004034635818915707</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004029262429875514</v>
+        <v>0.004029262429875494</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003991433644302064</v>
+        <v>0.003991433644302079</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004003305977001315</v>
+        <v>0.004003305977001236</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004000395781381293</v>
+        <v>0.004000395781381186</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003967950358619843</v>
+        <v>0.003967950358619844</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004034635818915697</v>
+        <v>0.004034635818915707</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004034635818915697</v>
+        <v>0.004034635818915707</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004034635818915697</v>
+        <v>0.004034635818915707</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004007395613767323</v>
+        <v>0.004007395613767281</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003342564401333394</v>
+        <v>0.003342564401333395</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004034646771984618</v>
+        <v>0.004034646771984556</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003973058372287607</v>
+        <v>0.00397305837228755</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004089984897578825</v>
+        <v>0.004089984897578766</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003977867844580205</v>
+        <v>0.003977867844580203</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004034635818915697</v>
+        <v>0.004034635818915707</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004087198068984612</v>
+        <v>0.004087198068984665</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000350741687479098</v>
+        <v>0.0003507416874789818</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005010415930555716</v>
+        <v>0.0005010415930555717</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004784139078128685</v>
+        <v>0.0004784139078127739</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0004001981722826191</v>
+        <v>0.000400198172282619</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0006668290790212195</v>
+        <v>0.0006668290790212188</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0005384672796432349</v>
+        <v>0.0005384672796431019</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005349888046782084</v>
+        <v>0.0005349888046780976</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005274196558827597</v>
+        <v>0.0005274196558826417</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0006128978653190863</v>
+        <v>0.0006128978653190628</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0006911416813499558</v>
+        <v>0.0006911416813498402</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001001294275846119</v>
+        <v>0.00100129427584609</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0005452668513426281</v>
+        <v>0.0005452668513426228</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0006495363604443713</v>
+        <v>0.0006495363604442984</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0008238423371610029</v>
+        <v>0.0008238423371609168</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0006463789566843197</v>
+        <v>0.000646378956684315</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0004502144995535258</v>
+        <v>0.0004502144995534126</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001149631171190345</v>
+        <v>0.001149631171190202</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0008098133678872952</v>
+        <v>0.000809813367887173</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0006399494988109381</v>
+        <v>0.0006399494988108776</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005558827735675867</v>
+        <v>0.0005558827735674939</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0006320778052091287</v>
+        <v>0.0006320778052091294</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0009628846823054485</v>
+        <v>0.0009628846823053591</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001814770671737202</v>
+        <v>0.001814770671737106</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001199835784020407</v>
+        <v>0.001199835784020302</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0005652997049494317</v>
+        <v>0.00056529970494937</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001188011070790972</v>
+        <v>0.001188011070790955</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0003482382169062466</v>
+        <v>0.0003482382169062463</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0002957412036069243</v>
+        <v>0.0002957412036068592</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003527569516071029</v>
+        <v>0.0003527569516071032</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0003514739142297792</v>
+        <v>0.0003514739142297469</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003125819331222263</v>
+        <v>0.000312581933122226</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003012004562311177</v>
+        <v>0.0003012004562311172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003214244286776511</v>
+        <v>0.0003214244286776126</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003514739142297792</v>
+        <v>0.0003514739142297469</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003514739142297792</v>
+        <v>0.0003514739142297469</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003074476041610309</v>
+        <v>0.0003074476041609752</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003514739142297792</v>
+        <v>0.0003514739142297469</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003514739142297792</v>
+        <v>0.0003514739142297469</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0003461005251895639</v>
+        <v>0.0003461005251895588</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003082717396161996</v>
+        <v>0.0003082717396161147</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002785380461510916</v>
+        <v>0.000278538046151032</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002756278505310969</v>
+        <v>0.0002756278505309909</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0002847884539339444</v>
+        <v>0.0002847884539338799</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0003514739142297792</v>
+        <v>0.0003514739142297469</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003514739142297792</v>
+        <v>0.0003514739142297469</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003514739142297792</v>
+        <v>0.0003514739142297469</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002826276829171088</v>
+        <v>0.0002826276829170887</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002876591887198315</v>
+        <v>0.0002876591887198311</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003098788411344061</v>
+        <v>0.0003098788411343564</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002482904414374415</v>
+        <v>0.0002482904414373517</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004068229928928905</v>
+        <v>0.0004068229928927957</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0002947059398942978</v>
+        <v>0.0002947059398942357</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003514739142297792</v>
+        <v>0.0003514739142297469</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004040361642987248</v>
+        <v>0.0004040361642987241</v>
       </c>
     </row>
   </sheetData>
@@ -1954,40 +1954,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004181343892456336</v>
+        <v>0.004181343892456404</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00132718889729462</v>
+        <v>0.001327188897294687</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003922043758503623</v>
+        <v>0.003922043758503614</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001836689858195504</v>
+        <v>0.001836689858195555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002204014092334162</v>
+        <v>0.002204014092334168</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00442310488991504</v>
+        <v>0.004423104889915024</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002065892180369799</v>
+        <v>0.002065892180369796</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003330981294063512</v>
+        <v>0.003330981294063505</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004616596736515901</v>
+        <v>0.00461659673651586</v>
       </c>
       <c r="K2" t="n">
         <v>0.007082893383117531</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004469601147336737</v>
+        <v>0.00446960114733707</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01386725500415722</v>
+        <v>0.01386725500415721</v>
       </c>
       <c r="N2" t="n">
         <v>0.004373821554773818</v>
@@ -1996,43 +1996,43 @@
         <v>0.003730186705965209</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004560590890329368</v>
+        <v>0.004560590890329373</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00237266948993962</v>
+        <v>0.002372669489939615</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002153926279214422</v>
+        <v>0.002153926279214417</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004334527718033303</v>
+        <v>0.004334527718033322</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004080815953800784</v>
+        <v>0.004080815953800782</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005998189378940365</v>
+        <v>0.005998189378940357</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00183869427227386</v>
+        <v>0.001838694272273848</v>
       </c>
       <c r="W2" t="n">
         <v>0.004641798095726461</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003513667682344517</v>
+        <v>0.003513667682344483</v>
       </c>
       <c r="Y2" t="n">
         <v>0.003268069955826281</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.002454082545880898</v>
+        <v>0.002454082545880912</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004869055108302466</v>
+        <v>0.00486905510830249</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007528614150134567</v>
+        <v>0.007528614150134629</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004821752541492052</v>
+        <v>0.000482175254149159</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006519191881347172</v>
+        <v>0.0006519191881346461</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006563401689343484</v>
+        <v>0.0006563401689343436</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005480380845706315</v>
+        <v>0.0005480380845706325</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005007913063965185</v>
+        <v>0.0005007913063965205</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006924543985924875</v>
+        <v>0.0006924543985924703</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006563401689343484</v>
+        <v>0.0006563401689343436</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006563401689343484</v>
+        <v>0.0006563401689343436</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006502760129209961</v>
+        <v>0.0006502760129209944</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006563401689343484</v>
+        <v>0.0006563401689343436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006563401689343484</v>
+        <v>0.0006563401689343436</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006789273988440684</v>
+        <v>0.0006789273988440705</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005213332228145426</v>
+        <v>0.0005213332228145314</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005584343038427611</v>
+        <v>0.0005584343038426914</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005493399323961393</v>
+        <v>0.0005493399323961248</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004479478732794237</v>
+        <v>0.000447947873279377</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006563401689343484</v>
+        <v>0.0006563401689343436</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006563401689343484</v>
+        <v>0.0006563401689343436</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006563401689343484</v>
+        <v>0.0006563401689343436</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005712517106587706</v>
+        <v>0.0005712517106587271</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005909601927069392</v>
+        <v>0.0005909601927069546</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0006563743973084067</v>
+        <v>0.0006563743973084007</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004639104337770035</v>
+        <v>0.0004639104337769909</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000829370003771593</v>
+        <v>0.0008293700037715461</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004789400514422985</v>
+        <v>0.0004789400514422586</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0006563401689343484</v>
+        <v>0.0006563401689343436</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008487733697520259</v>
+        <v>0.0008487733697520258</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005589550011093474</v>
+        <v>0.005589550011093466</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004546434445325152</v>
+        <v>0.004546434445325118</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005495038157123615</v>
+        <v>0.005495038157123602</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004725059785913531</v>
+        <v>0.004725059785913534</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004863423987727549</v>
+        <v>0.00486342398772754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005677669055766213</v>
+        <v>0.005677669055766207</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004818492702926103</v>
+        <v>0.004818492702926093</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005279602829441062</v>
+        <v>0.005279602829441046</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005619108909500922</v>
+        <v>0.005619108909500892</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006647130728725153</v>
+        <v>0.006647130728725149</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005694616395609792</v>
+        <v>0.005694616395609808</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009134305323438051</v>
+        <v>0.009134305323438048</v>
       </c>
       <c r="N4" t="n">
         <v>0.005659705858821384</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005425108514372616</v>
+        <v>0.005425108514372603</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00572778108847511</v>
+        <v>0.005727781088475102</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004930309429903256</v>
+        <v>0.004930309429903255</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004850580098206385</v>
+        <v>0.004850580098206371</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005645383716740981</v>
+        <v>0.005645383716740972</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005552908757912188</v>
+        <v>0.005552908757912179</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006251768856440067</v>
+        <v>0.006251768856440058</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003888925713879549</v>
+        <v>0.003888925713879579</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005757380161259203</v>
+        <v>0.005757380161259196</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005346189872757616</v>
+        <v>0.005346189872757638</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005256672385395824</v>
+        <v>0.005256672385395816</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004959983532793487</v>
+        <v>0.004959983532793464</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005840212673756581</v>
+        <v>0.00584021267375658</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006816265738198029</v>
+        <v>0.006816265738198035</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004241246480261762</v>
+        <v>0.004241246480261751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004300306565753633</v>
+        <v>0.004300306565753485</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004304727546553261</v>
+        <v>0.004304727546553204</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004255361346540385</v>
+        <v>0.004255361346540379</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004242619282505002</v>
+        <v>0.004242619282504993</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004317890759188966</v>
+        <v>0.004317890759188931</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004304727546553261</v>
+        <v>0.004304727546553204</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004304727546553261</v>
+        <v>0.004304727546553204</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004173431580639984</v>
+        <v>0.004173431580639968</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004304727546553261</v>
+        <v>0.004304727546553204</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004304727546553261</v>
+        <v>0.004304727546553204</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004327314776462973</v>
+        <v>0.004327314776462955</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004255519100024193</v>
+        <v>0.004255519100024169</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004269042008396085</v>
+        <v>0.004269042008396052</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004265727216795297</v>
+        <v>0.004265727216795253</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004228771001852922</v>
+        <v>0.004228771001852913</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004304727546553261</v>
+        <v>0.004304727546553204</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004304727546553261</v>
+        <v>0.004304727546553204</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004304727546553261</v>
+        <v>0.004304727546553204</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004273713802670932</v>
+        <v>0.004273713802670895</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003434141293510702</v>
+        <v>0.0034341412935107</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004304740022393672</v>
+        <v>0.004304740022393658</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004234589167712444</v>
+        <v>0.004234589167712438</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004367794889532537</v>
+        <v>0.004367794889532481</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004240067286864771</v>
+        <v>0.00424006728686474</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004304727546553261</v>
+        <v>0.004304727546553204</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004381542212399229</v>
+        <v>0.004381542212399224</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001698658097527804</v>
+        <v>0.001698658097527799</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006555425317594818</v>
+        <v>0.0006555425317594938</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001604146243557945</v>
+        <v>0.001604146243557913</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008341678723478645</v>
+        <v>0.0008341678723478811</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000972532074161883</v>
+        <v>0.0009725320741618864</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001744399115387817</v>
+        <v>0.001744399115387805</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009276007893604286</v>
+        <v>0.0009276007893603951</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001388710915875394</v>
+        <v>0.00138871091587536</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001812782619319661</v>
+        <v>0.00181278261931964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002756238815159483</v>
+        <v>0.002756238815159457</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00180372448204413</v>
+        <v>0.001803724482044117</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005243413409872374</v>
+        <v>0.005243413409872367</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001768813945255709</v>
+        <v>0.001768813945255681</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001491838573994218</v>
+        <v>0.001491838573994212</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001794511148096708</v>
+        <v>0.001794511148096707</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001039417516337586</v>
+        <v>0.00103941751633755</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0009596881846407119</v>
+        <v>0.000959688184640677</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00175449180317531</v>
+        <v>0.001754491803175283</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001662016844346513</v>
+        <v>0.001662016844346485</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002318498916061678</v>
+        <v>0.002318498916061677</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0007938221616010875</v>
+        <v>0.0007938221616010708</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001824110220880804</v>
+        <v>0.001824110220880803</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001412919932379218</v>
+        <v>0.00141291993237923</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001365780471830158</v>
+        <v>0.001365780471830129</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001069091619227811</v>
+        <v>0.001069091619227812</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001949320760190908</v>
+        <v>0.001949320760190884</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00292537382463236</v>
+        <v>0.00292537382463237</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003503545666960917</v>
+        <v>0.0003503545666960401</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0004094146521879607</v>
+        <v>0.000409414652187725</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004138356329875935</v>
+        <v>0.0004138356329875802</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003644694329747115</v>
+        <v>0.0003644694329747123</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003517273689393347</v>
+        <v>0.0003517273689393356</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003846208188105609</v>
+        <v>0.0003846208188105394</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004138356329875935</v>
+        <v>0.0004138356329875803</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004138356329875935</v>
+        <v>0.0004138356329875803</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003671052904587272</v>
+        <v>0.0003671052904587115</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004138356329875935</v>
+        <v>0.0004138356329875802</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004138356329875935</v>
+        <v>0.0004138356329875803</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0004364228628972946</v>
+        <v>0.0004364228628972966</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003646271864585231</v>
+        <v>0.0003646271864584847</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003357720680176952</v>
+        <v>0.0003357720680176583</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003324572764169037</v>
+        <v>0.0003324572764168683</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003378790882872534</v>
+        <v>0.0003378790882872006</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0004138356329875935</v>
+        <v>0.0004138356329875803</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004138356329875935</v>
+        <v>0.0004138356329875802</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004138356329875935</v>
+        <v>0.0004138356329875803</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0003404438622925381</v>
+        <v>0.000340443862292518</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000339037741232237</v>
+        <v>0.0003390377412322547</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000371470082015277</v>
+        <v>0.0003714700820152751</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0003013192273340494</v>
+        <v>0.0003013192273340544</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004769029759668638</v>
+        <v>0.0004769029759668318</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003491753732990958</v>
+        <v>0.000349175373299064</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0004138356329875935</v>
+        <v>0.0004138356329875802</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004906502988335608</v>
+        <v>0.0004906502988335621</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003291941411390164</v>
+        <v>0.003291941411390165</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001156469552318387</v>
+        <v>0.001156469552318388</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00456255996038311</v>
+        <v>0.004562559960383104</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001922549803031484</v>
+        <v>0.001922549803031482</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002117262526377829</v>
+        <v>0.002117262526377832</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004150727060845433</v>
+        <v>0.004150727060845429</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001458637754016211</v>
+        <v>0.001458637754016202</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004429433159541675</v>
+        <v>0.004429433159541664</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004380963665846312</v>
+        <v>0.004380963665846314</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005191822967126137</v>
+        <v>0.005191822967126133</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003691081394191447</v>
+        <v>0.003691081394191431</v>
       </c>
       <c r="M2" t="n">
         <v>0.01205201315286395</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002961954230551824</v>
+        <v>0.002961954230551811</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002885618488576273</v>
+        <v>0.002885618488576265</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004375963013555384</v>
+        <v>0.004375963013555375</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002119565085148881</v>
+        <v>0.00211956508514888</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00145689030969367</v>
+        <v>0.001456890309693662</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003964596958714042</v>
+        <v>0.003964596958714031</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003497743434602777</v>
+        <v>0.003497743434602768</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004210784666989121</v>
+        <v>0.004210784666989109</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002185230194765317</v>
+        <v>0.002185230194765333</v>
       </c>
       <c r="W2" t="n">
-        <v>0.004027499882859241</v>
+        <v>0.00402749988285922</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004368989270358217</v>
+        <v>0.004368989270358204</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.005260001168415388</v>
+        <v>0.005260001168415378</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.002401180521055884</v>
+        <v>0.002401180521055874</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004907372481934667</v>
+        <v>0.004907372481934655</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006971132975986957</v>
+        <v>0.00697113297598694</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004729411037272016</v>
+        <v>0.000472941103727208</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006391232406864048</v>
+        <v>0.0006391232406864047</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006436834827396592</v>
+        <v>0.0006436834827396624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005380464018734008</v>
+        <v>0.0005380464018734013</v>
       </c>
       <c r="F3" t="n">
         <v>0.0004911974863645283</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006790880273095503</v>
+        <v>0.0006790880273095565</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006436834827396592</v>
+        <v>0.0006436834827396624</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006436834827396592</v>
+        <v>0.0006436834827396624</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006379193096165975</v>
+        <v>0.000637919309616615</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006436834827396592</v>
+        <v>0.0006436834827396624</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006436834827396592</v>
+        <v>0.0006436834827396624</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006616945304572403</v>
+        <v>0.0006616945304572401</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005113295744214129</v>
+        <v>0.0005113295744214144</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005477015776256847</v>
+        <v>0.0005477015776257087</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005387859207707261</v>
+        <v>0.0005387859207707327</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004393863292524654</v>
+        <v>0.0004393863292524862</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006436834827396592</v>
+        <v>0.0006436834827396624</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006436834827396592</v>
+        <v>0.0006436834827396624</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006436834827396592</v>
+        <v>0.0006436834827396624</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005602354213990353</v>
+        <v>0.0005602354213990861</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005805213503110978</v>
+        <v>0.0005805213503111144</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0006437170384871696</v>
+        <v>0.0006437170384871837</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004550352075456373</v>
+        <v>0.0004550352075456529</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.000813258880786218</v>
+        <v>0.0008132588807861947</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004697694763795032</v>
+        <v>0.0004697694763794971</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0006436834827396592</v>
+        <v>0.0006436834827396624</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008310647043161787</v>
+        <v>0.0008310647043161712</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005253833996082719</v>
+        <v>0.005253833996082709</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00447258149205374</v>
+        <v>0.004472581492053744</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005716959536834339</v>
+        <v>0.005716959536834331</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004745350957870566</v>
+        <v>0.004745350957870573</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004820375080998969</v>
+        <v>0.004820375080998977</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005566851280938939</v>
+        <v>0.005566851280938929</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004585616340708342</v>
+        <v>0.004585616340708329</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005668436381181464</v>
+        <v>0.005668436381181459</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005532903749626974</v>
+        <v>0.005532903749626993</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00594631851361288</v>
+        <v>0.005946318513612871</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005399315832875471</v>
+        <v>0.005399315832875462</v>
       </c>
       <c r="M4" t="n">
-        <v>0.008458223512214907</v>
+        <v>0.0084582235122149</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005133557543572254</v>
+        <v>0.00513355754357224</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005105734062001703</v>
+        <v>0.00510573406200168</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005648947140847619</v>
+        <v>0.005648947140847608</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004826516591905637</v>
+        <v>0.004826516591905633</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004584979417772301</v>
+        <v>0.004584979417772292</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005499009044362042</v>
+        <v>0.005499009044362026</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005328846416894335</v>
+        <v>0.005328846416894334</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005588741573146282</v>
+        <v>0.005588741573146271</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004078113118480682</v>
+        <v>0.004078113118480778</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005521936421569542</v>
+        <v>0.005521936421569527</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005646405293342073</v>
+        <v>0.005646405293342068</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005971168667393962</v>
+        <v>0.005971168667393945</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004929162111398344</v>
+        <v>0.004929162111398333</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005842639651946834</v>
+        <v>0.005842639651946822</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006600592583604521</v>
+        <v>0.006600592583604502</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004226341486312448</v>
+        <v>0.004226341486312447</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004284014836450981</v>
+        <v>0.004284014836450978</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004288575078504246</v>
+        <v>0.004288575078504259</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004240715725808197</v>
+        <v>0.004240715725808193</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004227693468133842</v>
+        <v>0.004227693468133853</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004301479619258811</v>
+        <v>0.004301479619258838</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004288575078504246</v>
+        <v>0.004288575078504259</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004288575078504246</v>
+        <v>0.004288575078504259</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004168608034827186</v>
+        <v>0.004168608034827198</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004288575078504246</v>
+        <v>0.004288575078504259</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004288575078504246</v>
+        <v>0.004288575078504259</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004306586126221781</v>
+        <v>0.004306586126221789</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004240333633100305</v>
+        <v>0.004240333633100324</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004253590801166648</v>
+        <v>0.004253590801166661</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004250341148935929</v>
+        <v>0.004250341148935917</v>
       </c>
       <c r="Q5" t="n">
         <v>0.004214111165036457</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004288575078504246</v>
+        <v>0.004288575078504259</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004288575078504246</v>
+        <v>0.004288575078504259</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004288575078504246</v>
+        <v>0.004288575078504259</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004258159240042191</v>
+        <v>0.004258159240042208</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003493215588119746</v>
+        <v>0.003493215588119737</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004288587309180185</v>
+        <v>0.004288587309180203</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004219814997415915</v>
+        <v>0.004219814997415936</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004350383319837356</v>
+        <v>0.004350383319837346</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00422518546538734</v>
+        <v>0.004225185465387335</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004288575078504246</v>
+        <v>0.004288575078504259</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004362609798902363</v>
+        <v>0.004362609798902344</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00137184264158878</v>
+        <v>0.001371842641588767</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005905901375598075</v>
+        <v>0.0005905901375598077</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001834968182340401</v>
+        <v>0.00183496818234039</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008633596033766331</v>
+        <v>0.0008633596033766329</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009383837265050373</v>
+        <v>0.0009383837265050392</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001642675384058447</v>
+        <v>0.001642675384058431</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0007036249862144065</v>
+        <v>0.0007036249862143919</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001786445026687525</v>
+        <v>0.001786445026687509</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00172461694931408</v>
+        <v>0.001724616949314099</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002064327159118949</v>
+        <v>0.002064327159118938</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00151732447838153</v>
+        <v>0.001517324478381516</v>
       </c>
       <c r="M6" t="n">
-        <v>0.004576232157720983</v>
+        <v>0.004576232157720989</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001251566189078316</v>
+        <v>0.001251566189078301</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001181558165121223</v>
+        <v>0.001181558165121206</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001724771243967135</v>
+        <v>0.001724771243967114</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009445252374117053</v>
+        <v>0.0009445252374116959</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0007029880632783722</v>
+        <v>0.0007029880632783532</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001617017689868103</v>
+        <v>0.001617017689868092</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001446855062400408</v>
+        <v>0.001446855062400396</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001664565676265797</v>
+        <v>0.001664565676265785</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009184645815952428</v>
+        <v>0.0009184645815952612</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001597760524689062</v>
+        <v>0.001597760524689044</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001722229396461591</v>
+        <v>0.00172222939646157</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002089177312900027</v>
+        <v>0.002089177312900018</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001047170756904406</v>
+        <v>0.001047170756904389</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001960648297452892</v>
+        <v>0.001960648297452877</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002718601229110563</v>
+        <v>0.002718601229110558</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003443501318185144</v>
+        <v>0.0003443501318185003</v>
       </c>
       <c r="C7" t="n">
         <v>0.0004020234819570546</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004065837240103055</v>
+        <v>0.0004065837240103245</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003587243713142624</v>
+        <v>0.0003587243713142627</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003457021136399164</v>
+        <v>0.0003457021136399166</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003773037223783289</v>
+        <v>0.0003773037223783529</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004065837240103055</v>
+        <v>0.0004065837240103245</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004065837240103055</v>
+        <v>0.0004065837240103245</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003603212345142882</v>
+        <v>0.0003603212345142887</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004065837240103055</v>
+        <v>0.0004065837240103245</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004065837240103055</v>
+        <v>0.0004065837240103245</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0004245947717278462</v>
+        <v>0.0004245947717278467</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003583422786063648</v>
+        <v>0.0003583422786063879</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003294149042861634</v>
+        <v>0.0003294149042861677</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003261652520554483</v>
+        <v>0.0003261652520554339</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003321198105425274</v>
+        <v>0.0003321198105425162</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0004065837240103055</v>
+        <v>0.0004065837240103245</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004065837240103055</v>
+        <v>0.0004065837240103245</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004065837240103055</v>
+        <v>0.0004065837240103245</v>
       </c>
       <c r="U7" t="n">
-        <v>0.000333983343161714</v>
+        <v>0.0003339833431617221</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003335670512342953</v>
+        <v>0.0003335670512343018</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003644114122997005</v>
+        <v>0.0003644114122997175</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002956391005354366</v>
+        <v>0.0002956391005354527</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004683919653434189</v>
+        <v>0.0004683919653434032</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000343194110893401</v>
+        <v>0.0003431941108933985</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0004065837240103055</v>
+        <v>0.0004065837240103245</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004806184444084067</v>
+        <v>0.0004806184444084035</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002848947726453594</v>
+        <v>0.002848947726453514</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001041227118947209</v>
+        <v>0.001041227118947208</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003123128907899146</v>
+        <v>0.003123128907899076</v>
       </c>
       <c r="E2" t="n">
         <v>0.001367810645366252</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002383736899836471</v>
+        <v>0.002383736899836473</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00377372139235359</v>
+        <v>0.003773721392353525</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001419059932089072</v>
+        <v>0.001419059932088988</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004140893929793141</v>
+        <v>0.004140893929793051</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00409043448839817</v>
+        <v>0.004090434488398138</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006031072525237776</v>
+        <v>0.006031072525237701</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003289389212812771</v>
+        <v>0.003289389212812718</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01004788744583552</v>
+        <v>0.01004788744583557</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002032538638739209</v>
+        <v>0.002032538638739127</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002740430357329705</v>
+        <v>0.00274043035732962</v>
       </c>
       <c r="P2" t="n">
-        <v>0.003908425090301718</v>
+        <v>0.003908425090301674</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002009883658339749</v>
+        <v>0.002009883658339668</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002085582229832861</v>
+        <v>0.002085582229832777</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003717455744508775</v>
+        <v>0.003717455744508717</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003743103084071652</v>
+        <v>0.003743103084071577</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004157829225056085</v>
+        <v>0.004157829225055999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002995380470428253</v>
+        <v>0.002995380470428246</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002653046589766952</v>
+        <v>0.002653046589766868</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004718578632200703</v>
+        <v>0.004718578632200651</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007661002269914927</v>
+        <v>0.007661002269914902</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00209735958855529</v>
+        <v>0.002097359588555257</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.005266616099471769</v>
+        <v>0.005266616099471685</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006415043674791183</v>
+        <v>0.006415043674791187</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004655567214621887</v>
+        <v>0.0004655567214621591</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006305230431172778</v>
+        <v>0.0006305230431172782</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000634143949737114</v>
+        <v>0.000634143949737038</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005300630209493952</v>
+        <v>0.0005300630209493942</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004857467154609616</v>
+        <v>0.0004857467154609615</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006691016097621177</v>
+        <v>0.0006691016097620307</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000634143949737114</v>
+        <v>0.000634143949737038</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000634143949737114</v>
+        <v>0.000634143949737038</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006293795959392412</v>
+        <v>0.0006293795959392369</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000634143949737114</v>
+        <v>0.000634143949737038</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000634143949737114</v>
+        <v>0.000634143949737038</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006479078166152581</v>
+        <v>0.0006479078166153022</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000503460643789475</v>
+        <v>0.000503460643789452</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005393735509571866</v>
+        <v>0.0005393735509570911</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005305704296340674</v>
+        <v>0.0005305704296339677</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004324254832960546</v>
+        <v>0.0004324254832960273</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000634143949737114</v>
+        <v>0.000634143949737038</v>
       </c>
       <c r="S3" t="n">
-        <v>0.000634143949737114</v>
+        <v>0.000634143949737038</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000634143949737114</v>
+        <v>0.000634143949737038</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00055174984988495</v>
+        <v>0.000551749849884878</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005745449859017951</v>
+        <v>0.0005745449859017877</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0006341770819365238</v>
+        <v>0.000634177081936464</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004478768377422661</v>
+        <v>0.000447876837742245</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00080158005653496</v>
+        <v>0.0008015800565349101</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004624251271458488</v>
+        <v>0.0004624251271457707</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000634143949737114</v>
+        <v>0.000634143949737038</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008188112820518242</v>
+        <v>0.0008188112820518238</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005063376175856551</v>
+        <v>0.005063376175856501</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004402182113071861</v>
+        <v>0.004402182113071852</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005163311996895477</v>
+        <v>0.005163311996895426</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004514422893769674</v>
+        <v>0.004514422893769669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004889952241138951</v>
+        <v>0.004889952241138941</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005400445317836448</v>
+        <v>0.00540044531783641</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004542198865400882</v>
+        <v>0.004542198865400834</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005534275396175556</v>
+        <v>0.005534275396175505</v>
       </c>
       <c r="J4" t="n">
-        <v>0.005407345628346788</v>
+        <v>0.005407345628346761</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006223223298617458</v>
+        <v>0.006223223298617402</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005223911925709408</v>
+        <v>0.005223911925709377</v>
       </c>
       <c r="M4" t="n">
-        <v>0.007696052268377654</v>
+        <v>0.007696052268377686</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004765804650144181</v>
+        <v>0.004765804650144131</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005023822869086176</v>
+        <v>0.005023822869086126</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005449543233967853</v>
+        <v>0.00544954323396782</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004757547175816789</v>
+        <v>0.004757547175816736</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004785138416228516</v>
+        <v>0.004785138416228466</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005379937149901653</v>
+        <v>0.005379937149901568</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005389285304006019</v>
+        <v>0.005389285304005967</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005540448112434615</v>
+        <v>0.005540448112434567</v>
       </c>
       <c r="V4" t="n">
-        <v>0.004404296235982159</v>
+        <v>0.004404296235982183</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004991972511921553</v>
+        <v>0.004991972511921511</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005744834686686854</v>
+        <v>0.005744834686686816</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.006817313550950888</v>
+        <v>0.006817313550950852</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004789431125186159</v>
+        <v>0.004789431125186087</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005944587908126294</v>
+        <v>0.005944587908126246</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006368618717170291</v>
+        <v>0.006368618717170284</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004194658141727406</v>
+        <v>0.004194658141727341</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004252485300162608</v>
+        <v>0.004252485300162598</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004256106206782401</v>
+        <v>0.004256106206782356</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004209073721998999</v>
+        <v>0.004209073721998989</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004198157106260053</v>
+        <v>0.004198157106260048</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004268847863367982</v>
+        <v>0.004268847863367893</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004256106206782401</v>
+        <v>0.004256106206782356</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004256106206782401</v>
+        <v>0.004256106206782356</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004145831761803974</v>
+        <v>0.004145831761803952</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004256106206782401</v>
+        <v>0.004256106206782356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004256106206782401</v>
+        <v>0.004256106206782356</v>
       </c>
       <c r="M5" t="n">
-        <v>0.00426987007366052</v>
+        <v>0.004269870073660554</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004208473676325383</v>
+        <v>0.004208473676325314</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004221563509277339</v>
+        <v>0.004221563509277274</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004218354874926504</v>
+        <v>0.004218354874926463</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004182582194462521</v>
+        <v>0.004182582194462431</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004256106206782401</v>
+        <v>0.004256106206782356</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004256106206782401</v>
+        <v>0.004256106206782356</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004256106206782401</v>
+        <v>0.004256106206782356</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0042260745249067</v>
+        <v>0.004226074524906615</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003521930128757734</v>
+        <v>0.003521930128757775</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004256118283080072</v>
+        <v>0.004256118283079992</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004188214031719149</v>
+        <v>0.004188214031719108</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004317134701576185</v>
+        <v>0.004317134701576146</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004193516712372128</v>
+        <v>0.004193516712372063</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004256106206782401</v>
+        <v>0.004256106206782356</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004328857724295322</v>
+        <v>0.004328857724295317</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001207716168901027</v>
+        <v>0.001207716168900959</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005465221061163183</v>
+        <v>0.0005465221061163182</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001307651989939949</v>
+        <v>0.001307651989939888</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006587628868141262</v>
+        <v>0.0006587628868141269</v>
       </c>
       <c r="F6" t="n">
         <v>0.001034292234183402</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001502723952254895</v>
+        <v>0.001502723952254799</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0006865388584453629</v>
+        <v>0.0006865388584452949</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001678615389220032</v>
+        <v>0.001678615389219968</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001616804494948268</v>
+        <v>0.001616804494948243</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002367563291661913</v>
+        <v>0.002367563291661859</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001368251918753898</v>
+        <v>0.001368251918753835</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0038403922614221</v>
+        <v>0.003840392261422099</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0009101446431886547</v>
+        <v>0.0009101446431885908</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001126101503504595</v>
+        <v>0.001126101503504512</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001551821868386282</v>
+        <v>0.001551821868386213</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0009018871688612632</v>
+        <v>0.0009018871688612014</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0009294784092730005</v>
+        <v>0.0009294784092729321</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001524277142946129</v>
+        <v>0.001524277142946031</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001533625297050501</v>
+        <v>0.001533625297050429</v>
       </c>
       <c r="U6" t="n">
-        <v>0.00164272674685305</v>
+        <v>0.001642726746852961</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001213070644187812</v>
+        <v>0.001213070644187808</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001094251146339979</v>
+        <v>0.001094251146339895</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001847113321105225</v>
+        <v>0.001847113321105198</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00296165354399537</v>
+        <v>0.002961653543995327</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0009337711182306337</v>
+        <v>0.0009337711182305497</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002088927901170785</v>
+        <v>0.002088927901170719</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002512958710214753</v>
+        <v>0.002512958710214754</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.000338998134771836</v>
+        <v>0.0003389981347718066</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003968252932070562</v>
+        <v>0.000396825293207056</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004004461998269075</v>
+        <v>0.0004004461998268167</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003534137150434541</v>
+        <v>0.0003534137150434535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003424970993045133</v>
+        <v>0.0003424970993045129</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003711264977863307</v>
+        <v>0.0003711264977862856</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004004461998269075</v>
+        <v>0.0004004461998268167</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004004461998269075</v>
+        <v>0.0004004461998268167</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003552906284054379</v>
+        <v>0.0003552906284054321</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004004461998269075</v>
+        <v>0.0004004461998268167</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004004461998269075</v>
+        <v>0.0004004461998268167</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0004142100667049732</v>
+        <v>0.0004142100667049644</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003528136693698083</v>
+        <v>0.0003528136693697769</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003238421436957301</v>
+        <v>0.0003238421436956617</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003206335093449217</v>
+        <v>0.0003206335093448529</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003269221875069432</v>
+        <v>0.0003269221875068922</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0004004461998269075</v>
+        <v>0.0004004461998268167</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004004461998269075</v>
+        <v>0.0004004461998268167</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004004461998269075</v>
+        <v>0.0004004461998268167</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0003283531593251217</v>
+        <v>0.0003283531593250007</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000330704536963383</v>
+        <v>0.0003307045369633871</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003583969174984268</v>
+        <v>0.0003583969174983773</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002904926661375687</v>
+        <v>0.0002904926661375016</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004614746946206855</v>
+        <v>0.0004614746946206096</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003378567054165945</v>
+        <v>0.0003378567054165197</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0004004461998269075</v>
+        <v>0.0004004461998268167</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004731977173397759</v>
+        <v>0.0004731977173397752</v>
       </c>
     </row>
   </sheetData>
@@ -4009,82 +4009,82 @@
         <v>0.001135166563470815</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005465469486700951</v>
+        <v>0.0005465469486700945</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00233412665832154</v>
+        <v>0.002334126658321541</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001399647871259294</v>
+        <v>0.001399647871259295</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001142419254185225</v>
+        <v>0.001142419254185226</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001596317999658207</v>
+        <v>0.001596317999658209</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002134436665739084</v>
+        <v>0.002134436665739085</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002041316956140567</v>
+        <v>0.002041316956140569</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002047353501163617</v>
+        <v>0.002047353501163616</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003529490252789256</v>
+        <v>0.003529490252789261</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003061430713308717</v>
+        <v>0.003061430713308715</v>
       </c>
       <c r="M2" t="n">
-        <v>0.004883267199571429</v>
+        <v>0.004883267199571424</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002938201218983892</v>
+        <v>0.002938201218983891</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001401776257664075</v>
+        <v>0.001401776257664078</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002283895304619685</v>
+        <v>0.002283895304619688</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001960883208017415</v>
+        <v>0.001960883208017413</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002291168150980744</v>
+        <v>0.002291168150980745</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002126553086018564</v>
+        <v>0.002126553086018565</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00156990113383972</v>
+        <v>0.001569901133839721</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002562883568020682</v>
+        <v>0.002562883568020689</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001058113254164474</v>
+        <v>0.001058113254164471</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002944334145390386</v>
+        <v>0.002944334145390392</v>
       </c>
       <c r="X2" t="n">
-        <v>0.002556775410676256</v>
+        <v>0.002556775410676259</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001132588872208531</v>
+        <v>0.001132588872208529</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001896253909419627</v>
+        <v>0.001896253909419631</v>
       </c>
       <c r="AA2" t="n">
         <v>0.002783011492336839</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.002315206234657222</v>
+        <v>0.002315206234657224</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004254869627799696</v>
+        <v>0.0004254869627799757</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005815506384905917</v>
+        <v>0.0005815506384905916</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005836704355089838</v>
+        <v>0.0005836704355089895</v>
       </c>
       <c r="E3" t="n">
         <v>0.0004885756743552656</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000443251941596312</v>
+        <v>0.0004432519415963119</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006164708090475982</v>
+        <v>0.0006164708090476069</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005836704355089838</v>
+        <v>0.0005836704355089895</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005836704355089838</v>
+        <v>0.0005836704355089895</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005784480302026867</v>
+        <v>0.000578448030202687</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005836704355089838</v>
+        <v>0.0005836704355089895</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005836704355089838</v>
+        <v>0.0005836704355089895</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005861836721208267</v>
+        <v>0.0005861836721208272</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004610517806206884</v>
+        <v>0.0004610517806206911</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000494748451654888</v>
+        <v>0.000494748451654892</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004864885833596388</v>
+        <v>0.0004864885833596431</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0003944003000316396</v>
+        <v>0.0003944003000316407</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005836704355089838</v>
+        <v>0.0005836704355089895</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005836704355089838</v>
+        <v>0.0005836704355089895</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005836704355089838</v>
+        <v>0.0005836704355089895</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005063591290108397</v>
+        <v>0.0005063591290108398</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005271100857017973</v>
+        <v>0.000527110085701793</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0005837015230758666</v>
+        <v>0.0005837015230758716</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004088981296117118</v>
+        <v>0.0004088981296117131</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007407706375265402</v>
+        <v>0.0007407706375265396</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004225486235637304</v>
+        <v>0.000422548623563733</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0005836704355089838</v>
+        <v>0.0005836704355089895</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007465854261623687</v>
+        <v>0.0007465854261623672</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004283524091254544</v>
+        <v>0.004283524091254545</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004067631997683069</v>
+        <v>0.00406763199768307</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004720530966927381</v>
+        <v>0.00472053096692738</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004373018488968106</v>
+        <v>0.004373018488968105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004281796461993878</v>
+        <v>0.00428179646199388</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004451608374631288</v>
+        <v>0.004451608374631287</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004647746309509364</v>
+        <v>0.004647746309509374</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00461380526882755</v>
+        <v>0.004613805268827562</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004501933433136583</v>
+        <v>0.004501933433136587</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005156226960442861</v>
+        <v>0.005156226960442863</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004985624754534818</v>
+        <v>0.004985624754534819</v>
       </c>
       <c r="M4" t="n">
         <v>0.005651259952072188</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004940709050887194</v>
+        <v>0.004940709050887196</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004380700194098901</v>
+        <v>0.004380700194098903</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004702222228349396</v>
+        <v>0.004702222228349397</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004584488112137412</v>
+        <v>0.004584488112137417</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004704873095445927</v>
+        <v>0.004704873095445929</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004644872837274901</v>
+        <v>0.004644872837274903</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004441979737242951</v>
+        <v>0.004441979737242952</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004803910174313472</v>
+        <v>0.004803910174313473</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003508126077819118</v>
+        <v>0.003508126077819116</v>
       </c>
       <c r="W4" t="n">
-        <v>0.00494294443054591</v>
+        <v>0.004942944430545907</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004801683822687034</v>
+        <v>0.004801683822687037</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004282584553058218</v>
+        <v>0.00428258455305822</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004560931491714052</v>
+        <v>0.004560931491714055</v>
       </c>
       <c r="AA4" t="n">
         <v>0.004884144217854119</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004712159752198131</v>
+        <v>0.004712159752198132</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004024854210281345</v>
+        <v>0.004024854210281354</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004080390431588561</v>
+        <v>0.004080390431588563</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004082510228606951</v>
+        <v>0.00408251022860695</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00404094337154645</v>
+        <v>0.004040943371546452</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004026958186592311</v>
+        <v>0.004026958186592312</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004094465579600339</v>
+        <v>0.004094465579600346</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004082510228606951</v>
+        <v>0.00408251022860695</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004082510228606951</v>
+        <v>0.00408251022860695</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003966534637730214</v>
+        <v>0.003966534637730215</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004082510228606951</v>
+        <v>0.00408251022860695</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004082510228606951</v>
+        <v>0.00408251022860695</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004085023465218785</v>
+        <v>0.004085023465218787</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004037817168761107</v>
+        <v>0.004037817168761111</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004050099209666786</v>
+        <v>0.004050099209666795</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004047088584665435</v>
+        <v>0.004047088584665437</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004013523486747602</v>
+        <v>0.004013523486747606</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004082510228606951</v>
+        <v>0.00408251022860695</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004082510228606951</v>
+        <v>0.00408251022860695</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004082510228606951</v>
+        <v>0.00408251022860695</v>
       </c>
       <c r="U5" t="n">
         <v>0.00405433116522357</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003314581658268488</v>
+        <v>0.003314581658268486</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004082521559660027</v>
+        <v>0.004082521559660026</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004018807775387426</v>
+        <v>0.004018807775387424</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004139771407478644</v>
+        <v>0.004139771407478649</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004023783220140739</v>
+        <v>0.00402378322014075</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004082510228606951</v>
+        <v>0.00408251022860695</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004140415887177258</v>
+        <v>0.004140415887177261</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0005679271650591971</v>
+        <v>0.0005679271650591955</v>
       </c>
       <c r="C6" t="n">
         <v>0.0003520350714877192</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001004934040732043</v>
+        <v>0.001004934040732042</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000657421562772747</v>
+        <v>0.0006574215627727467</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005661995357985288</v>
+        <v>0.000566199535798529</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0006940269563734423</v>
+        <v>0.0006940269563734387</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009321493833140155</v>
+        <v>0.0009321493833140236</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008982083426321921</v>
+        <v>0.0008982083426322002</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008568011974665297</v>
+        <v>0.000856801197466534</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001440630034247514</v>
+        <v>0.001440630034247515</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001270027828339466</v>
+        <v>0.001270027828339462</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001935663025876843</v>
+        <v>0.001935663025876842</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001225112124691846</v>
+        <v>0.001225112124691845</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006231187758410505</v>
+        <v>0.0006231187758410515</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0009446408100915527</v>
+        <v>0.0009446408100915507</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0008688911859420589</v>
+        <v>0.0008688911859420604</v>
       </c>
       <c r="R6" t="n">
         <v>0.0009892761692505807</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009292759110795529</v>
+        <v>0.0009292759110795536</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0007263828110476016</v>
+        <v>0.0007263828110476015</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001046328756055623</v>
+        <v>0.001046328756055621</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0004920888494835835</v>
+        <v>0.0004920888494835831</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00118536301228806</v>
+        <v>0.001185363012288056</v>
       </c>
       <c r="X6" t="n">
         <v>0.001044102404429187</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0005669876268628724</v>
+        <v>0.0005669876268628738</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008453345655187065</v>
+        <v>0.0008453345655187066</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001168547291658774</v>
+        <v>0.001168547291658771</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0009965628260027821</v>
+        <v>0.000996562826002781</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003092572840859981</v>
+        <v>0.0003092572840860045</v>
       </c>
       <c r="C7" t="n">
         <v>0.0003647935053932122</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0003669133024116049</v>
+        <v>0.0003669133024116031</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000325346445351102</v>
+        <v>0.0003253464453511016</v>
       </c>
       <c r="F7" t="n">
         <v>0.0003113612603969609</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003368841613424976</v>
+        <v>0.0003368841613425043</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003669133024116049</v>
+        <v>0.0003669133024116031</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003669133024116049</v>
+        <v>0.0003669133024116031</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003214024020601654</v>
+        <v>0.0003214024020601644</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003669133024116049</v>
+        <v>0.0003669133024116031</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003669133024116049</v>
+        <v>0.0003669133024116031</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000369426539023442</v>
+        <v>0.0003694265390234422</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003222202425657611</v>
+        <v>0.0003222202425657592</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002925177914089378</v>
+        <v>0.0002925177914089452</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002895071664075907</v>
+        <v>0.0002895071664075936</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0002979265605522518</v>
+        <v>0.0002979265605522552</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0003669133024116049</v>
+        <v>0.0003669133024116031</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003669133024116049</v>
+        <v>0.0003669133024116031</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003669133024116049</v>
+        <v>0.0003669133024116031</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002967497469657253</v>
+        <v>0.0002967497469657247</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002985444299329517</v>
+        <v>0.0002985444299329497</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003249401414021852</v>
+        <v>0.000324940141402184</v>
       </c>
       <c r="X7" t="n">
-        <v>0.000261226357129581</v>
+        <v>0.0002612263571295759</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004241744812832924</v>
+        <v>0.0004241744812832992</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003081862939453954</v>
+        <v>0.000308186293945401</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003669133024116049</v>
+        <v>0.0003669133024116031</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004248189609819108</v>
+        <v>0.0004248189609819114</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0009779793719861924</v>
+        <v>0.0009779793719861757</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009902744588774987</v>
+        <v>0.0009902744588775028</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0009218574307705862</v>
+        <v>0.0009218574307705716</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001671115428959285</v>
+        <v>0.001671115428959283</v>
       </c>
       <c r="F2" t="n">
         <v>0.001671314803919373</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001332633635069161</v>
+        <v>0.001332633635069125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00147515005988784</v>
+        <v>0.001475150059887824</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001447993887301784</v>
+        <v>0.001447993887301772</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001512258550985866</v>
+        <v>0.001512258550985853</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001117180328694684</v>
+        <v>0.001117180328694669</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001703066722296804</v>
+        <v>0.001703066722296786</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008069544752529042</v>
+        <v>0.0008069544752529026</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00168680524057032</v>
+        <v>0.001686805240570307</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001743357386965158</v>
+        <v>0.001743357386965141</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001583780500182623</v>
+        <v>0.001583780500182606</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000778643464755837</v>
+        <v>0.0007786434647558248</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002850167355344122</v>
+        <v>0.002850167355344101</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001613676212621606</v>
+        <v>0.001613676212621589</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00101403574503009</v>
+        <v>0.001014035745030092</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0006768085338412915</v>
+        <v>0.0006768085338412741</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001493964791930323</v>
+        <v>0.001493964791930301</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002808652264877877</v>
+        <v>0.002808652264877859</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004465112338012779</v>
+        <v>0.004465112338012763</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00147121751036752</v>
+        <v>0.001471217510367503</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001918544358322845</v>
+        <v>0.001918544358322824</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.002224010686666448</v>
+        <v>0.002224010686666433</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0004392035935216758</v>
+        <v>0.000439203593521675</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000413726712302406</v>
+        <v>0.0004137267123024105</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000566531618334297</v>
+        <v>0.0005665316183342725</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005672586399665402</v>
+        <v>0.0005672586399665072</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000475879037559724</v>
+        <v>0.0004758790375597216</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004330944992618165</v>
+        <v>0.0004330944992618148</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005990944853340299</v>
+        <v>0.0005990944853340326</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005672586399665402</v>
+        <v>0.0005672586399665072</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005672586399665402</v>
+        <v>0.0005672586399665072</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005621329889789426</v>
+        <v>0.0005621329889789268</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005672586399665402</v>
+        <v>0.0005672586399665072</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005672586399665402</v>
+        <v>0.0005672586399665072</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005589399889765875</v>
+        <v>0.0005589399889765847</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004482457106904258</v>
+        <v>0.0004482457106904225</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0004809514970190683</v>
+        <v>0.000480951497019041</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004729345185082033</v>
+        <v>0.0004729345185082006</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0003835541843253966</v>
+        <v>0.0003835541843254036</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005672586399665402</v>
+        <v>0.0005672586399665072</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005672586399665402</v>
+        <v>0.0005672586399665072</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005672586399665402</v>
+        <v>0.0005672586399665072</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004922202228397438</v>
+        <v>0.0004922202228397379</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005134983247556667</v>
+        <v>0.0005134983247556453</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0005672888133728392</v>
+        <v>0.0005672888133728177</v>
       </c>
       <c r="X3" t="n">
-        <v>0.000397625690558296</v>
+        <v>0.0003976256905582781</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007197382486444108</v>
+        <v>0.0007197382486443909</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004108747779238088</v>
+        <v>0.0004108747779237992</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0005672586399665402</v>
+        <v>0.0005672586399665072</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007192402207425292</v>
+        <v>0.0007192402207425255</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004211990630312996</v>
+        <v>0.004211990630312981</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004216010014324272</v>
+        <v>0.004216010014324238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004191534841757009</v>
+        <v>0.004191534841756996</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004458511635416313</v>
+        <v>0.004458511635416314</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00446181123485662</v>
+        <v>0.004461811234856618</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004341257944646097</v>
+        <v>0.004341257944646088</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004393203507980174</v>
+        <v>0.004393203507980158</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004383305401956437</v>
+        <v>0.004383305401956419</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004304538323127127</v>
+        <v>0.004304538323127131</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004262727744453079</v>
+        <v>0.004262727744453067</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004476276455095661</v>
+        <v>0.004476276455095646</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004144367463342808</v>
+        <v>0.004144367463342809</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004470349335958329</v>
+        <v>0.00447034933595831</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004490961929250415</v>
+        <v>0.0044909619292504</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004432798027864586</v>
+        <v>0.004432798027864579</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004139335032847926</v>
+        <v>0.004139335032847948</v>
       </c>
       <c r="R4" t="n">
-        <v>0.004894381165905715</v>
+        <v>0.004894381165905698</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004443694663995424</v>
+        <v>0.00444369466399541</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004225132754892189</v>
+        <v>0.004225132754892185</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004102217396335705</v>
+        <v>0.004102217396335687</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003732576740776702</v>
+        <v>0.003732576740776716</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004879249402925573</v>
+        <v>0.00487924940292556</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005483009648447022</v>
+        <v>0.005483009648447005</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004391770139858342</v>
+        <v>0.00439177013985833</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004554815523161012</v>
+        <v>0.004554815523160997</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004666154412875524</v>
+        <v>0.004666154412875512</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004010277838502625</v>
+        <v>0.004010277838502626</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0040063271616475</v>
+        <v>0.004006327161647447</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004061560724785922</v>
+        <v>0.004061560724785874</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004062287746418162</v>
+        <v>0.004062287746418142</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004022862005925489</v>
+        <v>0.004022862005925491</v>
       </c>
       <c r="F5" t="n">
         <v>0.004010494473725852</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004073891538219241</v>
+        <v>0.004073891538219232</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004062287746418162</v>
+        <v>0.004062287746418142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004062287746418162</v>
+        <v>0.004062287746418142</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003958228712713247</v>
+        <v>0.003958228712713245</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004062287746418162</v>
+        <v>0.004062287746418142</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004062287746418162</v>
+        <v>0.004062287746418142</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004053969095428231</v>
+        <v>0.004053969095428232</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004018908931217394</v>
+        <v>0.004018908931217393</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004030829806283436</v>
+        <v>0.004030829806283444</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004027907711756352</v>
+        <v>0.004027907711756356</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003995329629503599</v>
+        <v>0.003995329629503588</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004062287746418162</v>
+        <v>0.004062287746418142</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004062287746418162</v>
+        <v>0.004062287746418142</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004062287746418162</v>
+        <v>0.004062287746418142</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004034937124521025</v>
+        <v>0.004034937124521027</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003375208226710068</v>
+        <v>0.003375208226710077</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004062298744270446</v>
+        <v>0.004062298744270438</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004000458528289529</v>
+        <v>0.004000458528289502</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004117864773275279</v>
+        <v>0.004117864773275259</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004005287665055608</v>
+        <v>0.004005287665055606</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004062287746418162</v>
+        <v>0.004062287746418142</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004112347900768534</v>
+        <v>0.004112347900768533</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000507560062555534</v>
+        <v>0.0005075600625555217</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005115794465668122</v>
+        <v>0.000511579446566798</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0004871042739995525</v>
+        <v>0.0004871042739995382</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0007540810676588593</v>
+        <v>0.0007540810676588586</v>
       </c>
       <c r="F6" t="n">
         <v>0.0007573806670991666</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0005950957723159007</v>
+        <v>0.0005950957723158782</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0006887729402227163</v>
+        <v>0.0006887729402227015</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006788748341989754</v>
+        <v>0.000678874834198964</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0006589790750273049</v>
+        <v>0.000658979075027292</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0005582971766956201</v>
+        <v>0.000558297176695606</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0007718458873382101</v>
+        <v>0.0007718458873381985</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0004399368955853536</v>
+        <v>0.0004399368955853526</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0007659187682008614</v>
+        <v>0.0007659187682008543</v>
       </c>
       <c r="O6" t="n">
-        <v>0.000744799756920193</v>
+        <v>0.0007447997569201812</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0006866358555343703</v>
+        <v>0.0006866358555343563</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0004349044650904701</v>
+        <v>0.0004349044650904889</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001189950598148255</v>
+        <v>0.001189950598148242</v>
       </c>
       <c r="S6" t="n">
-        <v>0.000739264096237958</v>
+        <v>0.0007392640962379468</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005207021871347266</v>
+        <v>0.0005207021871347228</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0003560552240054896</v>
+        <v>0.0003560552240054785</v>
       </c>
       <c r="V6" t="n">
-        <v>0.000649043478344421</v>
+        <v>0.0006490434783444227</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001133087230595355</v>
+        <v>0.00113308723059534</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001736847476116804</v>
+        <v>0.001736847476116788</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0006873395721008869</v>
+        <v>0.0006873395721008742</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008503849554035531</v>
+        <v>0.000850384955403537</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0009617238451180716</v>
+        <v>0.0009617238451180582</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0003058472707451715</v>
+        <v>0.0003058472707451709</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003018965938900447</v>
+        <v>0.0003018965938899944</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003571301570284674</v>
+        <v>0.000357130157028433</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0003578571786606981</v>
+        <v>0.0003578571786606851</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003184314381680331</v>
+        <v>0.0003184314381680319</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003060639059683938</v>
+        <v>0.0003060639059683928</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003277293658890281</v>
+        <v>0.0003277293658890121</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003578571786606981</v>
+        <v>0.0003578571786606852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003578571786606981</v>
+        <v>0.0003578571786606851</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000312669464613419</v>
+        <v>0.0003126694646133997</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003578571786606981</v>
+        <v>0.0003578571786606851</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003578571786606981</v>
+        <v>0.0003578571786606852</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0003495385276707711</v>
+        <v>0.00034953852767077</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003144783634599387</v>
+        <v>0.0003144783634599301</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002846676339532333</v>
+        <v>0.0002846676339532325</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002817455394261351</v>
+        <v>0.0002817455394261342</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0002908990617461286</v>
+        <v>0.0002908990617461298</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0003578571786606981</v>
+        <v>0.0003578571786606851</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003578571786606981</v>
+        <v>0.0003578571786606852</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003578571786606981</v>
+        <v>0.0003578571786606851</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002887749521908059</v>
+        <v>0.0002887749521908049</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002916749642778</v>
+        <v>0.0002916749642777889</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003161365719402295</v>
+        <v>0.0003161365719402179</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002542963559592953</v>
+        <v>0.0002542963559592781</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004134342055178203</v>
+        <v>0.0004134342055178035</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003008570972981585</v>
+        <v>0.0003008570972981457</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003578571786606981</v>
+        <v>0.0003578571786606852</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004079173330110741</v>
+        <v>0.0004079173330110728</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001444449762968629</v>
+        <v>0.00144444976296862</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001100923944573057</v>
+        <v>0.001100923944573058</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001132788476677038</v>
+        <v>0.001132788476677023</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002047553845860406</v>
+        <v>0.002047553845860408</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00146162958268367</v>
+        <v>0.001461629582683671</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0009811459276413391</v>
+        <v>0.0009811459276413271</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001040071893197619</v>
+        <v>0.001040071893197631</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009594093688666901</v>
+        <v>0.0009594093688666806</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001361535886422062</v>
+        <v>0.00136153588642208</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008418864853465593</v>
+        <v>0.000841886485346548</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001875464871632605</v>
+        <v>0.001875464871632599</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007392685293311448</v>
+        <v>0.0007392685293311506</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001249589720584641</v>
+        <v>0.00124958972058463</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00273022434597221</v>
+        <v>0.002730224345972196</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001915108116501154</v>
+        <v>0.001915108116501158</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0007238526046352867</v>
+        <v>0.0007238526046352756</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002884135835955677</v>
+        <v>0.00288413583595567</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001490506359148111</v>
+        <v>0.001490506359148086</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0008553381702089787</v>
+        <v>0.0008553381702089653</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007366015906235981</v>
+        <v>0.0007366015906235843</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001613526212691106</v>
+        <v>0.001613526212691108</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002453564944424754</v>
+        <v>0.002453564944424745</v>
       </c>
       <c r="X2" t="n">
-        <v>0.005382203624489805</v>
+        <v>0.005382203624489801</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.001393895581683859</v>
+        <v>0.001393895581683851</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001617307734501686</v>
+        <v>0.001617307734501666</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.002355027757544616</v>
+        <v>0.002355027757544613</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.000634184396421146</v>
+        <v>0.0006341843964211294</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004071337453279566</v>
+        <v>0.0004071337453279615</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005594936601751869</v>
+        <v>0.0005594936601751864</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005591910334256189</v>
+        <v>0.0005591910334256069</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004702788691746514</v>
+        <v>0.0004702788691746512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000426405722840525</v>
+        <v>0.0004264057228405249</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005907211026727274</v>
+        <v>0.0005907211026727166</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005591910334256189</v>
+        <v>0.0005591910334256069</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005591910334256189</v>
+        <v>0.0005591910334256069</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005546118052236131</v>
+        <v>0.0005546118052236221</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005591910334256189</v>
+        <v>0.0005591910334256069</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005591910334256189</v>
+        <v>0.0005591910334256069</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005515385588986839</v>
+        <v>0.0005515385588986885</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004413211965157102</v>
+        <v>0.0004413211965156956</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0004737128511376006</v>
+        <v>0.0004737128511375515</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004657728738984364</v>
+        <v>0.0004657728738984277</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000377251017682372</v>
+        <v>0.0003772510176823549</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0005591910334256189</v>
+        <v>0.0005591910334256069</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0005591910334256189</v>
+        <v>0.0005591910334256069</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005591910334256189</v>
+        <v>0.0005591910334256069</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004848769687392622</v>
+        <v>0.0004848769687392611</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005070957915197654</v>
+        <v>0.000507095791519765</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0005592209170244675</v>
+        <v>0.0005592209170244189</v>
       </c>
       <c r="X3" t="n">
-        <v>0.000391187370269723</v>
+        <v>0.0003911873702697263</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007102123117487654</v>
+        <v>0.0007102123117487439</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004043092031362491</v>
+        <v>0.0004043092031362481</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0005591910334256189</v>
+        <v>0.0005591910334256069</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007113044927378633</v>
+        <v>0.0007113044927378739</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004360276330922724</v>
+        <v>0.004360276330922714</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004235257526854335</v>
+        <v>0.004235257526854336</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004246679451781037</v>
+        <v>0.004246679451781019</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004575050819468772</v>
+        <v>0.004575050819468774</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004363731263740072</v>
+        <v>0.004363731263740071</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004191407523334236</v>
+        <v>0.004191407523334221</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004212885345835892</v>
+        <v>0.004212885345835878</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004183484802904435</v>
+        <v>0.004183484802904423</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004228222442032845</v>
+        <v>0.004228222442032837</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004140649091884723</v>
+        <v>0.004140649091884694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.004517376276795813</v>
+        <v>0.004517376276795803</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004098382814496248</v>
+        <v>0.004098382814496253</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00428925213363591</v>
+        <v>0.004289252133635896</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004828926068100097</v>
+        <v>0.004828926068100084</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004531825774035925</v>
+        <v>0.004531825774035905</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004097627128389274</v>
+        <v>0.00409762712838926</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00488502499887911</v>
+        <v>0.004885024998879097</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004377063419406284</v>
+        <v>0.004377063419406267</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004145552073059415</v>
+        <v>0.004145552073059403</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004102273984075855</v>
+        <v>0.004102273984075834</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003755288935829175</v>
+        <v>0.003755288935829189</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004728086964934759</v>
+        <v>0.004728086964934749</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005795541374006849</v>
+        <v>0.005795541374006816</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.004341849925481593</v>
+        <v>0.004341849925481578</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004423281031745746</v>
+        <v>0.004423281031745727</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004692171317399028</v>
+        <v>0.004692171317399005</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004060671514938051</v>
+        <v>0.004060671514938018</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003982186823272373</v>
+        <v>0.003982186823272363</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004037912545986704</v>
+        <v>0.004037912545986705</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004037609919237126</v>
+        <v>0.004037609919237122</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004000152611764697</v>
+        <v>0.004000152611764696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003986404323039552</v>
+        <v>0.003986404323039547</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00404910225923292</v>
+        <v>0.004049102259232931</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004037609919237126</v>
+        <v>0.004037609919237122</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004037609919237126</v>
+        <v>0.004037609919237122</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003934108089816963</v>
+        <v>0.003934108089816949</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004037609919237126</v>
+        <v>0.004037609919237122</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004037609919237126</v>
+        <v>0.004037609919237122</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004029957444710221</v>
+        <v>0.004029957444710226</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003994647747780955</v>
+        <v>0.00399464774778095</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004006454125528604</v>
+        <v>0.004006454125528615</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004003560097060912</v>
+        <v>0.004003560097060876</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00397129491994625</v>
+        <v>0.003971294919946231</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004037609919237126</v>
+        <v>0.004037609919237122</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004037609919237126</v>
+        <v>0.004037609919237122</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004037609919237126</v>
+        <v>0.004037609919237122</v>
       </c>
       <c r="U5" t="n">
-        <v>0.00401052331529876</v>
+        <v>0.004010523315298745</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003352008039674168</v>
+        <v>0.003352008039674195</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004037620811457985</v>
+        <v>0.004037620811457979</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003976374556815443</v>
+        <v>0.003976374556815412</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004092655401804542</v>
+        <v>0.004092655401804522</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003981157310810925</v>
+        <v>0.003981157310810924</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004037609919237126</v>
+        <v>0.004037609919237122</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004088780884455601</v>
+        <v>0.004088780884455578</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0006747227319323642</v>
+        <v>0.0006747227319323245</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005497039278639461</v>
+        <v>0.0005497039278639459</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0005611258527906692</v>
+        <v>0.0005611258527906331</v>
       </c>
       <c r="E6" t="n">
         <v>0.0008894972204783865</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0006781776647496831</v>
+        <v>0.0006781776647496834</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0004642676481482265</v>
+        <v>0.0004642676481482198</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005273317468455234</v>
+        <v>0.0005273317468454853</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004979312039140761</v>
+        <v>0.0004979312039140355</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0006016570954505335</v>
+        <v>0.0006016570954505198</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0004550954928943584</v>
+        <v>0.0004550954928943099</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008318226778054485</v>
+        <v>0.0008318226778054088</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0004128292155058516</v>
+        <v>0.0004128292155058561</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0006036985346455413</v>
+        <v>0.000603698534645503</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001101786192914089</v>
+        <v>0.001101786192914076</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0008046858988499171</v>
+        <v>0.0008046858988498953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0004120735293989005</v>
+        <v>0.0004120735293988662</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001199471399888742</v>
+        <v>0.001199471399888706</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0006915098204159208</v>
+        <v>0.0006915098204158764</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0004599984740690463</v>
+        <v>0.0004599984740690124</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0003751341088898447</v>
+        <v>0.0003751341088898277</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0006906675059747961</v>
+        <v>0.0006906675059747963</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001000947089748755</v>
+        <v>0.001000947089748742</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002068401498820842</v>
+        <v>0.002068401498820806</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.000656296326491233</v>
+        <v>0.0006562963264911896</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0007377274327553635</v>
+        <v>0.0007377274327553384</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001006617718408654</v>
+        <v>0.001006617718408611</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0003751179159476609</v>
+        <v>0.000375117915947643</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0002966332242819682</v>
+        <v>0.0002966332242819725</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003523589469963136</v>
+        <v>0.0003523589469963132</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0003520563202467422</v>
+        <v>0.0003520563202467343</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003145990127743055</v>
+        <v>0.0003145990127743051</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00030085072404916</v>
+        <v>0.0003008507240491598</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003219623840469199</v>
+        <v>0.0003219623840469305</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003520563202467422</v>
+        <v>0.0003520563202467343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003520563202467422</v>
+        <v>0.0003520563202467343</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003075427432346456</v>
+        <v>0.0003075427432346377</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003520563202467422</v>
+        <v>0.0003520563202467343</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003520563202467422</v>
+        <v>0.0003520563202467343</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000344403845719828</v>
+        <v>0.0003444038457198335</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003090941487905992</v>
+        <v>0.0003090941487905651</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0002793142503426098</v>
+        <v>0.000279314250342616</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002764202218749043</v>
+        <v>0.0002764202218748747</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0002857413209558574</v>
+        <v>0.0002857413209558464</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0003520563202467422</v>
+        <v>0.0003520563202467343</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003520563202467422</v>
+        <v>0.0003520563202467343</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003520563202467422</v>
+        <v>0.0003520563202467343</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0002833834401127557</v>
+        <v>0.0002833834401127403</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002873866098198043</v>
+        <v>0.000287386609819804</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003104809362719741</v>
+        <v>0.0003104809362719724</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002492346816294325</v>
+        <v>0.0002492346816294023</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.000407101802814171</v>
+        <v>0.0004071018028141329</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.000295603711820527</v>
+        <v>0.0002956037118205371</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003520563202467422</v>
+        <v>0.0003520563202467343</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004032272854652118</v>
+        <v>0.0004032272854651909</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002816313231164352</v>
+        <v>0.002816313231164419</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009020195333267541</v>
+        <v>0.0009020195333270136</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00313113746245043</v>
+        <v>0.003131137462450505</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001605936224443959</v>
+        <v>0.001605936224444013</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00186075970258617</v>
+        <v>0.001860759702586172</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004264383089671273</v>
+        <v>0.004264383089671342</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002052828941049464</v>
+        <v>0.00205282894104953</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003606771283960625</v>
+        <v>0.003606771283960682</v>
       </c>
       <c r="J2" t="n">
-        <v>0.004219226784472551</v>
+        <v>0.004219226784472571</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00519589228575908</v>
+        <v>0.005195892285759136</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00420801257253049</v>
+        <v>0.004208012572530552</v>
       </c>
       <c r="M2" t="n">
         <v>0.01359745738297558</v>
       </c>
       <c r="N2" t="n">
-        <v>0.005214400096641246</v>
+        <v>0.005214400096641311</v>
       </c>
       <c r="O2" t="n">
-        <v>0.002706330476785295</v>
+        <v>0.002706330476785354</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004008070619857284</v>
+        <v>0.004008070619857325</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.002377265436186649</v>
+        <v>0.002377265436186713</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002793613162487196</v>
+        <v>0.002793613162487153</v>
       </c>
       <c r="S2" t="n">
-        <v>0.003306599887480087</v>
+        <v>0.003306599887480152</v>
       </c>
       <c r="T2" t="n">
-        <v>0.003345854184167468</v>
+        <v>0.003345854184167535</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004695339175615911</v>
+        <v>0.004695339175615998</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001607844715000164</v>
+        <v>0.001607844715000169</v>
       </c>
       <c r="W2" t="n">
-        <v>0.003021609966365586</v>
+        <v>0.003021609966365666</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004245305458621643</v>
+        <v>0.004245305458621721</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.002999807108895628</v>
+        <v>0.002999807108895691</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.002529618603879394</v>
+        <v>0.002529618603879453</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.004364544185357897</v>
+        <v>0.004364544185357962</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006558133888164644</v>
+        <v>0.006558133888164648</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004723349212588636</v>
+        <v>0.0004723349212589628</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006378739032177508</v>
+        <v>0.0006378739032178077</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006428029332401875</v>
+        <v>0.0006428029332402515</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005368137942118969</v>
+        <v>0.0005368137942119469</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004898744840173289</v>
+        <v>0.0004898744840173283</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006781505860188549</v>
+        <v>0.0006781505860188706</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006428029332401875</v>
+        <v>0.0006428029332402515</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006428029332401875</v>
+        <v>0.0006428029332402515</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006368813369109085</v>
+        <v>0.0006368813369109201</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006428029332401875</v>
+        <v>0.0006428029332402515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006428029332401875</v>
+        <v>0.0006428029332402515</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006653203377060732</v>
+        <v>0.0006653203377060723</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005106617052717366</v>
+        <v>0.0005106617052717925</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0005469752620693867</v>
+        <v>0.0005469752620694248</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005380739318409202</v>
+        <v>0.000538073931841001</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0004388340661677041</v>
+        <v>0.0004388340661677173</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0006428029332401875</v>
+        <v>0.0006428029332402515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0006428029332401875</v>
+        <v>0.0006428029332402515</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0006428029332401875</v>
+        <v>0.0006428029332402515</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005594993151838866</v>
+        <v>0.000559499315183886</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0005788138802283782</v>
+        <v>0.0005788138802283978</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0006428364350670042</v>
+        <v>0.0006428364350671054</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004544577981775214</v>
+        <v>0.0004544577981776091</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0008121235454188855</v>
+        <v>0.0008121235454189202</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004691683904195267</v>
+        <v>0.0004691683904195374</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0006428029332401875</v>
+        <v>0.0006428029332402515</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0008286489428887669</v>
+        <v>0.0008286489428887695</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005072186986314891</v>
+        <v>0.005072186986315049</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00437131695576575</v>
+        <v>0.004371316955765972</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005186936721765895</v>
+        <v>0.005186936721766081</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004621346322655824</v>
+        <v>0.00462134632265591</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004718168306892056</v>
+        <v>0.004718168306892092</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005599991445645909</v>
+        <v>0.005599991445646027</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004793905927853182</v>
+        <v>0.004793905927853326</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005360299664532053</v>
+        <v>0.005360299664532255</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00545399768952331</v>
+        <v>0.005453997689523318</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005939515609286656</v>
+        <v>0.005939515609286798</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005579445054084084</v>
+        <v>0.005579445054084226</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009016097506014528</v>
+        <v>0.009016097506014632</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005946261489023547</v>
+        <v>0.005946261489023665</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005032099563826424</v>
+        <v>0.005032099563826562</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005506568560171681</v>
+        <v>0.005506568560171812</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00491215922060505</v>
+        <v>0.00491215922060518</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00506391307783974</v>
+        <v>0.005063913077839865</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005250890715305388</v>
+        <v>0.00525089071530551</v>
       </c>
       <c r="T4" t="n">
-        <v>0.005265198445500724</v>
+        <v>0.005265198445500879</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005757069878430842</v>
+        <v>0.005757069878430983</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003781612775137496</v>
+        <v>0.00378161277513749</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005147015235579766</v>
+        <v>0.005147015235579948</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005593037873149171</v>
+        <v>0.005593037873149321</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005139068350054041</v>
+        <v>0.005139068350054219</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004967690161207803</v>
+        <v>0.004967690161207976</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.005636498988872698</v>
+        <v>0.005636498988872872</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.006440979634606599</v>
+        <v>0.00644097963460666</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004217834416737298</v>
+        <v>0.004217834416737526</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004275038975345628</v>
+        <v>0.004275038975345754</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004279968005368054</v>
+        <v>0.004279968005368157</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004231663751105641</v>
+        <v>0.004231663751105791</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00421849674247066</v>
+        <v>0.004218496742470706</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004292851809732769</v>
+        <v>0.0042928518097329</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004279968005368054</v>
+        <v>0.004279968005368157</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004279968005368054</v>
+        <v>0.004279968005368157</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004148274839911161</v>
+        <v>0.004148274839911321</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004279968005368054</v>
+        <v>0.004279968005368157</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004279968005368054</v>
+        <v>0.004279968005368157</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004302485409833911</v>
+        <v>0.004302485409833965</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004231804079454196</v>
+        <v>0.004231804079454313</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004245039944491636</v>
+        <v>0.004245039944491667</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004241795514148048</v>
+        <v>0.004241795514148134</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004205623748443479</v>
+        <v>0.00420562374844363</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004279968005368054</v>
+        <v>0.004279968005368157</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004279968005368054</v>
+        <v>0.004279968005368157</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004279968005368054</v>
+        <v>0.004279968005368157</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004249604814787019</v>
+        <v>0.00424960481478717</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003406543119353309</v>
+        <v>0.003406543119353329</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004279980216390509</v>
+        <v>0.004279980216390631</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004211318415297971</v>
+        <v>0.00421131841529814</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004341683380244194</v>
+        <v>0.004341683380244227</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004216680253429686</v>
+        <v>0.00421668025342985</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004279968005368054</v>
+        <v>0.004279968005368157</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004352649651062511</v>
+        <v>0.004352649651062611</v>
       </c>
     </row>
     <row r="6">
@@ -6410,82 +6410,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001198490140792695</v>
+        <v>0.00119849014079277</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004976201102436252</v>
+        <v>0.000497620110243677</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001313239876243698</v>
+        <v>0.001313239876243785</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0007476494771336051</v>
+        <v>0.0007476494771336529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008444714613698305</v>
+        <v>0.0008444714613698292</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001683990856148501</v>
+        <v>0.00168399085614857</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000920209082330993</v>
+        <v>0.0009202090823310663</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001486602819009855</v>
+        <v>0.001486602819009927</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00166547716069209</v>
+        <v>0.001665477160692142</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002065818763764466</v>
+        <v>0.002065818763764527</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001705748208561918</v>
+        <v>0.001705748208561981</v>
       </c>
       <c r="M6" t="n">
         <v>0.005142400660492332</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002072564643501325</v>
+        <v>0.002072564643501393</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001116098974329042</v>
+        <v>0.001116098974329119</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001590567970674274</v>
+        <v>0.001590567970674313</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001038462375082827</v>
+        <v>0.001038462375082901</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001190216232317539</v>
+        <v>0.001190216232317625</v>
       </c>
       <c r="S6" t="n">
-        <v>0.001377193869783193</v>
+        <v>0.001377193869783263</v>
       </c>
       <c r="T6" t="n">
-        <v>0.001391501599978523</v>
+        <v>0.001391501599978594</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001841069288933455</v>
+        <v>0.001841069288933513</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0007073741921951493</v>
+        <v>0.000707374192195139</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001231014646082373</v>
+        <v>0.001231014646082481</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001677037283651758</v>
+        <v>0.00167703728365184</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001265371504531849</v>
+        <v>0.001265371504531919</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.001093993315685611</v>
+        <v>0.001093993315685682</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001762802143350499</v>
+        <v>0.001762802143350569</v>
       </c>
       <c r="AB6" t="n">
         <v>0.002567282789084376</v>
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003441375712151024</v>
+        <v>0.0003441375712152017</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0004013421298233904</v>
+        <v>0.0004013421298234607</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004062711598458429</v>
+        <v>0.0004062711598459112</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003579669055834336</v>
+        <v>0.0003579669055834768</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003447998969484666</v>
+        <v>0.0003447998969484665</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003768512202353721</v>
+        <v>0.0003768512202354435</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004062711598458429</v>
+        <v>0.0004062711598459112</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0004062711598458429</v>
+        <v>0.0004062711598459112</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003597543110799443</v>
+        <v>0.0003597543110799788</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0004062711598458429</v>
+        <v>0.0004062711598459112</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004062711598458429</v>
+        <v>0.0004062711598459112</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0004287885643117035</v>
+        <v>0.0004287885643117043</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003581072339319869</v>
+        <v>0.0003581072339320288</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003290393549942158</v>
+        <v>0.0003290393549942211</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003257949246506322</v>
+        <v>0.0003257949246506622</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003319269029212839</v>
+        <v>0.0003319269029213483</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0004062711598458429</v>
+        <v>0.0004062711598459112</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0004062711598458429</v>
+        <v>0.0004062711598459112</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004062711598458429</v>
+        <v>0.0004062711598459112</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0003336042252895954</v>
+        <v>0.0003336042252896689</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003323045364109759</v>
+        <v>0.000332304536410961</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003639796268931259</v>
+        <v>0.0003639796268932055</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002953178258005438</v>
+        <v>0.0002953178258006407</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004679865347219656</v>
+        <v>0.0004679865347219593</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003429834079074488</v>
+        <v>0.0003429834079075378</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0004062711598458429</v>
+        <v>0.0004062711598459112</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004789528055403165</v>
+        <v>0.0004789528055403169</v>
       </c>
     </row>
   </sheetData>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0006481345047574289</v>
+        <v>0.0006481345047574334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001030970720999978</v>
+        <v>0.001030970720999979</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001170879101715147</v>
+        <v>0.001170879101715151</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001222220553642456</v>
+        <v>0.001222220553642458</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001393705292544715</v>
+        <v>0.001393705292544714</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003975246046197948</v>
+        <v>0.003975246046197952</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00124711175729398</v>
+        <v>0.001247111757293982</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001311008226398386</v>
+        <v>0.001311008226398391</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002433593287065096</v>
+        <v>0.002433593287065088</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001953880173084583</v>
+        <v>0.001953880173084587</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003446437854085603</v>
+        <v>0.003446437854085606</v>
       </c>
       <c r="M2" t="n">
         <v>0.001946660567731257</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001862285406588474</v>
+        <v>0.001862285406588478</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001383143563793765</v>
+        <v>0.001383143563793769</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002904504670082234</v>
+        <v>0.002904504670082236</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001524100134807379</v>
+        <v>0.001524100134807385</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002829895539582968</v>
+        <v>0.002829895539582971</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00212217853678348</v>
+        <v>0.002122178536783485</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001487638465332802</v>
+        <v>0.001487638465332803</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001249201562415993</v>
+        <v>0.001249201562416</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001244415615733441</v>
+        <v>0.00124441561573344</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002896495298522785</v>
+        <v>0.002896495298522787</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004301053695401626</v>
+        <v>0.004301053695401632</v>
       </c>
       <c r="Y2" t="n">
         <v>0.004608571070029138</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001270410530130981</v>
+        <v>0.001270410530130985</v>
       </c>
       <c r="AA2" t="n">
         <v>0.001858518001328075</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004408567892258942</v>
+        <v>0.004408567892258943</v>
       </c>
     </row>
     <row r="3">
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004387819617636484</v>
+        <v>0.0004387819617636527</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005981442579786667</v>
+        <v>0.0005981442579786662</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000598657146875502</v>
+        <v>0.0005986571468755066</v>
       </c>
       <c r="E3" t="n">
         <v>0.0005024421386394956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004576422513866145</v>
+        <v>0.0004576422513866148</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006318083079970857</v>
+        <v>0.0006318083079970905</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000598657146875502</v>
+        <v>0.0005986571468755066</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000598657146875502</v>
+        <v>0.0005986571468755066</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005931956368427262</v>
+        <v>0.0005931956368427288</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000598657146875502</v>
+        <v>0.0005986571468755066</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000598657146875502</v>
+        <v>0.0005986571468755066</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0005932844156401949</v>
+        <v>0.0005932844156401951</v>
       </c>
       <c r="N3" t="n">
-        <v>0.000474727131872731</v>
+        <v>0.0004747271318727342</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000508784176051646</v>
+        <v>0.0005087841760516488</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0005004359715909146</v>
+        <v>0.0005004359715909211</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000407362838921356</v>
+        <v>0.0004073628389213608</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000598657146875502</v>
+        <v>0.0005986571468755066</v>
       </c>
       <c r="S3" t="n">
-        <v>0.000598657146875502</v>
+        <v>0.0005986571468755066</v>
       </c>
       <c r="T3" t="n">
-        <v>0.000598657146875502</v>
+        <v>0.0005986571468755066</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005204982479087435</v>
+        <v>0.0005204982479087464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000541849183509981</v>
+        <v>0.0005418491835099811</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0005986885669102952</v>
+        <v>0.0005986885669103006</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004220157173015003</v>
+        <v>0.0004220157173015031</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007574019321900681</v>
+        <v>0.0007574019321900725</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004358121981216767</v>
+        <v>0.0004358121981216807</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.000598657146875502</v>
+        <v>0.0005986571468755066</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0007705315389120859</v>
+        <v>0.000770531538912087</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.004208750491139381</v>
+        <v>0.004208750491139387</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004347963849553386</v>
+        <v>0.004347963849553387</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004399284758353501</v>
+        <v>0.004399284758353506</v>
       </c>
       <c r="E4" t="n">
         <v>0.004410952711923358</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0044766597328769</v>
+        <v>0.004476659732876901</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005421443579078222</v>
+        <v>0.005421443579078224</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00442707066614294</v>
+        <v>0.004427070666142945</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00445036017882128</v>
+        <v>0.004450360178821288</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004739765274269029</v>
+        <v>0.004739765274269035</v>
       </c>
       <c r="K4" t="n">
-        <v>0.004684679454404862</v>
+        <v>0.00468467945440487</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005228699202632575</v>
+        <v>0.005228699202632581</v>
       </c>
       <c r="M4" t="n">
         <v>0.004678633559240641</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004651294237577094</v>
+        <v>0.004651294237577101</v>
       </c>
       <c r="O4" t="n">
-        <v>0.004476652662245994</v>
+        <v>0.004476652662246001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.005031170920764084</v>
+        <v>0.005031170920764092</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.004528029677184838</v>
+        <v>0.004528029677184847</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005003976768801749</v>
+        <v>0.005003976768801754</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004746022231713954</v>
+        <v>0.004746022231713961</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004514739826815883</v>
+        <v>0.004514739826815893</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004427832375570189</v>
+        <v>0.004427832375570199</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003641965736843215</v>
+        <v>0.003641965736843195</v>
       </c>
       <c r="W4" t="n">
-        <v>0.005028251598881455</v>
+        <v>0.00502825159888146</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005540196641386385</v>
+        <v>0.005540196641386391</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.005652283113386791</v>
+        <v>0.005652283113386795</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004435562795254028</v>
+        <v>0.004435562795254032</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004649921062598784</v>
+        <v>0.00464992106259879</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.005582480130883628</v>
+        <v>0.005582480130883629</v>
       </c>
     </row>
     <row r="5">
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004132443947559827</v>
+        <v>0.004132443947559829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004190203686287056</v>
+        <v>0.004190203686287058</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004190716575183884</v>
+        <v>0.004190716575183887</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004148601931719653</v>
+        <v>0.004148601931719655</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004135475746181949</v>
+        <v>0.004135475746181953</v>
       </c>
       <c r="G5" t="n">
         <v>0.004202799784132119</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004190716575183884</v>
+        <v>0.004190716575183887</v>
       </c>
       <c r="I5" t="n">
-        <v>0.004190716575183884</v>
+        <v>0.004190716575183887</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004068961941803288</v>
+        <v>0.004068961941803295</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004190716575183884</v>
+        <v>0.004190716575183887</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004190716575183884</v>
+        <v>0.004190716575183887</v>
       </c>
       <c r="M5" t="n">
-        <v>0.004185343843948583</v>
+        <v>0.004185343843948581</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004145545539975089</v>
+        <v>0.004145545539975092</v>
       </c>
       <c r="O5" t="n">
-        <v>0.004157958932660295</v>
+        <v>0.0041579589326603</v>
       </c>
       <c r="P5" t="n">
-        <v>0.004154916110163931</v>
+        <v>0.004154916110163938</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.004120992046225777</v>
+        <v>0.004120992046225783</v>
       </c>
       <c r="R5" t="n">
-        <v>0.004190716575183884</v>
+        <v>0.004190716575183887</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004190716575183884</v>
+        <v>0.004190716575183887</v>
       </c>
       <c r="T5" t="n">
-        <v>0.004190716575183884</v>
+        <v>0.004190716575183887</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004162228574298638</v>
+        <v>0.004162228574298641</v>
       </c>
       <c r="V5" t="n">
-        <v>0.003385888522249335</v>
+        <v>0.003385888522249305</v>
       </c>
       <c r="W5" t="n">
-        <v>0.004190728027417609</v>
+        <v>0.004190728027417617</v>
       </c>
       <c r="X5" t="n">
-        <v>0.004126332848332556</v>
+        <v>0.00412633284833256</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004248577185355666</v>
+        <v>0.004248577185355671</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.004131361503585051</v>
+        <v>0.004131361503585054</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.004190716575183884</v>
+        <v>0.004190716575183887</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004256458600068402</v>
+        <v>0.004256458600068406</v>
       </c>
     </row>
     <row r="6">
@@ -7094,82 +7094,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0003971109124350586</v>
+        <v>0.0003971109124350624</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005363242708490672</v>
+        <v>0.0005363242708490664</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000587645179649177</v>
+        <v>0.00058764517964918</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0005993131332190384</v>
+        <v>0.0005993131332190387</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0006650201541725762</v>
+        <v>0.0006650201541725761</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00156787538183956</v>
+        <v>0.001567875381839563</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0006154310874386252</v>
+        <v>0.0006154310874386269</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0006387206001169592</v>
+        <v>0.0006387206001169625</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001004166341742028</v>
+        <v>0.001004166341742032</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008730398757005469</v>
+        <v>0.00087303987570055</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001417059623928253</v>
+        <v>0.001417059623928257</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0008669939805363159</v>
+        <v>0.0008669939805363162</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0008396546588727674</v>
+        <v>0.0008396546588727739</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0006230844650073335</v>
+        <v>0.0006230844650073385</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00117760272352542</v>
+        <v>0.001177602723525425</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0007163900984805154</v>
+        <v>0.000716390098480518</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001192337190097422</v>
+        <v>0.001192337190097425</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0009343826530096321</v>
+        <v>0.0009343826530096353</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0007031002481115688</v>
+        <v>0.0007031002481115752</v>
       </c>
       <c r="U6" t="n">
-        <v>0.000574264178331524</v>
+        <v>0.0005742641783315306</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0005668551680476402</v>
+        <v>0.0005668551680476403</v>
       </c>
       <c r="W6" t="n">
-        <v>0.001174683401642788</v>
+        <v>0.001174683401642794</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001686628444147732</v>
+        <v>0.001686628444147736</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.00184064353468247</v>
+        <v>0.001840643534682475</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0006239232165497084</v>
+        <v>0.000623923216549711</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0008382814838944577</v>
+        <v>0.0008382814838944603</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001770840552179307</v>
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0003208043688555055</v>
+        <v>0.0003208043688555057</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003785641075827326</v>
+        <v>0.000378564107582733</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0003790769964795706</v>
+        <v>0.0003790769964795701</v>
       </c>
       <c r="E7" t="n">
         <v>0.0003369623530153346</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0003238361674776307</v>
+        <v>0.0003238361674776304</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0003492315868934541</v>
+        <v>0.0003492315868934574</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0003790769964795706</v>
+        <v>0.0003790769964795701</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003790769964795706</v>
+        <v>0.0003790769964795701</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003333630092762817</v>
+        <v>0.0003333630092762843</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0003790769964795706</v>
+        <v>0.0003790769964795701</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0003790769964795706</v>
+        <v>0.0003790769964795701</v>
       </c>
       <c r="M7" t="n">
         <v>0.0003737042652442611</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0003339059612707699</v>
+        <v>0.000333905961270768</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003043907354216344</v>
+        <v>0.0003043907354216373</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003013479129252654</v>
+        <v>0.0003013479129252681</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003093524675214566</v>
+        <v>0.0003093524675214581</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0003790769964795706</v>
+        <v>0.0003790769964795701</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0003790769964795706</v>
+        <v>0.0003790769964795701</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003790769964795706</v>
+        <v>0.0003790769964795701</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0003086603770599711</v>
+        <v>0.000308660377059973</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000310777953453759</v>
+        <v>0.0003107779534537594</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0003371598301789547</v>
+        <v>0.0003371598301789578</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0002727646510938884</v>
+        <v>0.0002727646510938936</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0004369376066513472</v>
+        <v>0.0004369376066513464</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003197219248807308</v>
+        <v>0.000319721924880732</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003790769964795706</v>
+        <v>0.0003790769964795701</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0004448190213640817</v>
+        <v>0.0004448190213640818</v>
       </c>
     </row>
   </sheetData>
